--- a/配置表格/S神通真意表.xlsx
+++ b/配置表格/S神通真意表.xlsx
@@ -10,8 +10,9 @@
     <sheet name="神通真意" sheetId="1" r:id="rId1"/>
     <sheet name="字段说明" sheetId="2" r:id="rId2"/>
     <sheet name="枚举与注册" sheetId="3" r:id="rId3"/>
+    <sheet name="真意激活道具清单" sheetId="4" r:id="rIdConfig4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -263,7 +264,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -437,8 +438,36 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Microsoft YaHei"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -637,8 +666,30 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF17365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF17365D"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -744,8 +795,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
@@ -891,8 +956,10 @@
     <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="9"/>
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="10"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -905,6 +972,28 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="9" xfId="49"/>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="9" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="10" xfId="50"/>
+    <xf numFmtId="0" fontId="28" fillId="37" borderId="10" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="37" borderId="10" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="39" borderId="10" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="39" borderId="10" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1251,7 +1340,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K144"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -1389,103 +1478,4624 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" ht="34.5" customHeight="1" spans="1:11">
+    <row r="5">
       <c r="A5" s="7"/>
-      <c r="B5" s="7">
+      <c r="B5" t="n" s="7">
+        <v>92010001</v>
+      </c>
+      <c r="C5" t="str" s="7">
+        <v>青萍剑诀·庚金真意</v>
+      </c>
+      <c r="D5" t="n" s="7">
+        <v>100100</v>
+      </c>
+      <c r="E5" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F5" t="n" s="7">
+        <v>10202000</v>
+      </c>
+      <c r="G5" t="str" s="3">
+        <v>青萍剑诀：剑诀改为金行，物理伤害通道保持。</v>
+      </c>
+      <c r="H5" t="n" s="7">
+        <v>82010001</v>
+      </c>
+      <c r="I5" t="n" s="7">
         <v>1</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="7">
+      <c r="J5" t="n" s="7">
+        <v>10703100</v>
+      </c>
+      <c r="K5" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7"/>
+      <c r="B6" t="n" s="7">
+        <v>92010002</v>
+      </c>
+      <c r="C6" t="str" s="7">
+        <v>青萍剑诀·离火真意</v>
+      </c>
+      <c r="D6" t="n" s="7">
         <v>100100</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="7">
-        <v>20001</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="7">
+      <c r="E6" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F6" t="n" s="7">
+        <v>10202000</v>
+      </c>
+      <c r="G6" t="str" s="3">
+        <v>青萍剑诀：剑诀改为火行，物理伤害通道保持。</v>
+      </c>
+      <c r="H6" t="n" s="7">
+        <v>82010002</v>
+      </c>
+      <c r="I6" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n" s="7">
+        <v>10703101</v>
+      </c>
+      <c r="K6" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7"/>
+      <c r="B7" t="n" s="7">
+        <v>92010003</v>
+      </c>
+      <c r="C7" t="str" s="7">
+        <v>青萍剑诀·长锋真意</v>
+      </c>
+      <c r="D7" t="n" s="7">
+        <v>100100</v>
+      </c>
+      <c r="E7" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F7" t="n" s="7">
+        <v>10202000</v>
+      </c>
+      <c r="G7" t="str" s="3">
+        <v>青萍剑诀：扇形打击半径提高20%。</v>
+      </c>
+      <c r="H7" t="n" s="7">
+        <v>82010003</v>
+      </c>
+      <c r="I7" t="n" s="7">
         <v>2</v>
       </c>
-      <c r="I5" s="7">
+      <c r="J7" t="n" s="7">
+        <v>10703102</v>
+      </c>
+      <c r="K7" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7"/>
+      <c r="B8" t="n" s="7">
+        <v>92010004</v>
+      </c>
+      <c r="C8" t="str" s="7">
+        <v>青萍剑诀·聚锋真意</v>
+      </c>
+      <c r="D8" t="n" s="7">
+        <v>100100</v>
+      </c>
+      <c r="E8" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F8" t="n" s="7">
+        <v>10202000</v>
+      </c>
+      <c r="G8" t="str" s="3">
+        <v>青萍剑诀：扇形由180度收为90度，伤害系数提高20%。</v>
+      </c>
+      <c r="H8" t="n" s="7">
+        <v>82010004</v>
+      </c>
+      <c r="I8" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J8" t="n" s="7">
+        <v>10703103</v>
+      </c>
+      <c r="K8" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7"/>
+      <c r="B9" t="n" s="7">
+        <v>92010005</v>
+      </c>
+      <c r="C9" t="str" s="7">
+        <v>青萍剑诀·影锋真意</v>
+      </c>
+      <c r="D9" t="n" s="7">
+        <v>100100</v>
+      </c>
+      <c r="E9" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F9" t="n" s="7">
+        <v>10202000</v>
+      </c>
+      <c r="G9" t="str" s="3">
+        <v>青萍剑诀：原斩击每个命中目标额外承受一次系数30%的物理伤害，不新增飞剑实体。</v>
+      </c>
+      <c r="H9" t="n" s="7">
+        <v>82010005</v>
+      </c>
+      <c r="I9" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J9" t="n" s="7">
+        <v>10703104</v>
+      </c>
+      <c r="K9" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7"/>
+      <c r="B10" t="n" s="7">
+        <v>92010006</v>
+      </c>
+      <c r="C10" t="str" s="7">
+        <v>玄门伏虎击·庚金真意</v>
+      </c>
+      <c r="D10" t="n" s="7">
+        <v>100200</v>
+      </c>
+      <c r="E10" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F10" t="n" s="7">
+        <v>10202001</v>
+      </c>
+      <c r="G10" t="str" s="3">
+        <v>玄门伏虎击：拳劲改为金行，仍走物理伤害。</v>
+      </c>
+      <c r="H10" t="n" s="7">
+        <v>82010006</v>
+      </c>
+      <c r="I10" t="n" s="7">
         <v>1</v>
       </c>
-      <c r="J5" s="7">
-        <v>0</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" ht="17.25" customHeight="1" spans="1:11">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7">
+      <c r="J10" t="n" s="7">
+        <v>10703105</v>
+      </c>
+      <c r="K10" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7"/>
+      <c r="B11" t="n" s="7">
+        <v>92010007</v>
+      </c>
+      <c r="C11" t="str" s="7">
+        <v>玄门伏虎击·离火真意</v>
+      </c>
+      <c r="D11" t="n" s="7">
+        <v>100200</v>
+      </c>
+      <c r="E11" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F11" t="n" s="7">
+        <v>10202001</v>
+      </c>
+      <c r="G11" t="str" s="3">
+        <v>玄门伏虎击：拳劲改为火行，仍走物理伤害。</v>
+      </c>
+      <c r="H11" t="n" s="7">
+        <v>82010007</v>
+      </c>
+      <c r="I11" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n" s="7">
+        <v>10703106</v>
+      </c>
+      <c r="K11" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7"/>
+      <c r="B12" t="n" s="7">
+        <v>92010008</v>
+      </c>
+      <c r="C12" t="str" s="7">
+        <v>玄门伏虎击·震圈真意</v>
+      </c>
+      <c r="D12" t="n" s="7">
+        <v>100200</v>
+      </c>
+      <c r="E12" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F12" t="n" s="7">
+        <v>10202001</v>
+      </c>
+      <c r="G12" t="str" s="3">
+        <v>玄门伏虎击：落拳圆形范围提高25%。</v>
+      </c>
+      <c r="H12" t="n" s="7">
+        <v>82010008</v>
+      </c>
+      <c r="I12" t="n" s="7">
         <v>2</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="7">
-        <v>100100</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="7">
-        <v>20001</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H6" s="7">
-        <v>4</v>
-      </c>
-      <c r="I6" s="7">
+      <c r="J12" t="n" s="7">
+        <v>10703107</v>
+      </c>
+      <c r="K12" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7"/>
+      <c r="B13" t="n" s="7">
+        <v>92010009</v>
+      </c>
+      <c r="C13" t="str" s="7">
+        <v>玄门伏虎击·重拳真意</v>
+      </c>
+      <c r="D13" t="n" s="7">
+        <v>100200</v>
+      </c>
+      <c r="E13" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F13" t="n" s="7">
+        <v>10202001</v>
+      </c>
+      <c r="G13" t="str" s="3">
+        <v>玄门伏虎击：伤害系数提高20%，冷却时间提高15%。</v>
+      </c>
+      <c r="H13" t="n" s="7">
+        <v>82010009</v>
+      </c>
+      <c r="I13" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J13" t="n" s="7">
+        <v>10703108</v>
+      </c>
+      <c r="K13" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7"/>
+      <c r="B14" t="n" s="7">
+        <v>92010010</v>
+      </c>
+      <c r="C14" t="str" s="7">
+        <v>玄门伏虎击·余震真意</v>
+      </c>
+      <c r="D14" t="n" s="7">
+        <v>100200</v>
+      </c>
+      <c r="E14" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F14" t="n" s="7">
+        <v>10202001</v>
+      </c>
+      <c r="G14" t="str" s="3">
+        <v>玄门伏虎击：每个本次命中目标在300毫秒后额外承受系数30%的物理伤害，不重新圈人。</v>
+      </c>
+      <c r="H14" t="n" s="7">
+        <v>82010010</v>
+      </c>
+      <c r="I14" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J14" t="n" s="7">
+        <v>10703109</v>
+      </c>
+      <c r="K14" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7"/>
+      <c r="B15" t="n" s="7">
+        <v>92010011</v>
+      </c>
+      <c r="C15" t="str" s="7">
+        <v>太白藏锋斩·庚金真意</v>
+      </c>
+      <c r="D15" t="n" s="7">
+        <v>100300</v>
+      </c>
+      <c r="E15" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F15" t="n" s="7">
+        <v>10202002</v>
+      </c>
+      <c r="G15" t="str" s="3">
+        <v>太白藏锋斩：刀芒改为金行，不改变物理伤害通道。</v>
+      </c>
+      <c r="H15" t="n" s="7">
+        <v>82010011</v>
+      </c>
+      <c r="I15" t="n" s="7">
         <v>1</v>
       </c>
-      <c r="J6" s="7">
-        <v>0</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" ht="17.25" customHeight="1" spans="1:11">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7">
-        <v>3</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="7">
-        <v>100100</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="7">
-        <v>20001</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" s="7">
-        <v>12</v>
-      </c>
-      <c r="I7" s="7">
+      <c r="J15" t="n" s="7">
+        <v>10703110</v>
+      </c>
+      <c r="K15" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7"/>
+      <c r="B16" t="n" s="7">
+        <v>92010012</v>
+      </c>
+      <c r="C16" t="str" s="7">
+        <v>太白藏锋斩·离火真意</v>
+      </c>
+      <c r="D16" t="n" s="7">
+        <v>100300</v>
+      </c>
+      <c r="E16" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F16" t="n" s="7">
+        <v>10202002</v>
+      </c>
+      <c r="G16" t="str" s="3">
+        <v>太白藏锋斩：刀芒改为火行，不改变物理伤害通道。</v>
+      </c>
+      <c r="H16" t="n" s="7">
+        <v>82010012</v>
+      </c>
+      <c r="I16" t="n" s="7">
         <v>1</v>
       </c>
-      <c r="J7" s="7">
-        <v>0</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>38</v>
+      <c r="J16" t="n" s="7">
+        <v>10703111</v>
+      </c>
+      <c r="K16" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7"/>
+      <c r="B17" t="n" s="7">
+        <v>92010013</v>
+      </c>
+      <c r="C17" t="str" s="7">
+        <v>太白藏锋斩·远芒真意</v>
+      </c>
+      <c r="D17" t="n" s="7">
+        <v>100300</v>
+      </c>
+      <c r="E17" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F17" t="n" s="7">
+        <v>10202002</v>
+      </c>
+      <c r="G17" t="str" s="3">
+        <v>太白藏锋斩：弹道射程提高25%。</v>
+      </c>
+      <c r="H17" t="n" s="7">
+        <v>82010013</v>
+      </c>
+      <c r="I17" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n" s="7">
+        <v>10703112</v>
+      </c>
+      <c r="K17" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7"/>
+      <c r="B18" t="n" s="7">
+        <v>92010014</v>
+      </c>
+      <c r="C18" t="str" s="7">
+        <v>太白藏锋斩·贯锋真意</v>
+      </c>
+      <c r="D18" t="n" s="7">
+        <v>100300</v>
+      </c>
+      <c r="E18" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F18" t="n" s="7">
+        <v>10202002</v>
+      </c>
+      <c r="G18" t="str" s="3">
+        <v>太白藏锋斩：弹道命中后还可穿过一个目标。</v>
+      </c>
+      <c r="H18" t="n" s="7">
+        <v>82010014</v>
+      </c>
+      <c r="I18" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n" s="7">
+        <v>10703113</v>
+      </c>
+      <c r="K18" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7"/>
+      <c r="B19" t="n" s="7">
+        <v>92010015</v>
+      </c>
+      <c r="C19" t="str" s="7">
+        <v>太白藏锋斩·疾芒真意</v>
+      </c>
+      <c r="D19" t="n" s="7">
+        <v>100300</v>
+      </c>
+      <c r="E19" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F19" t="n" s="7">
+        <v>10202002</v>
+      </c>
+      <c r="G19" t="str" s="3">
+        <v>太白藏锋斩：弹道速度提高30%。</v>
+      </c>
+      <c r="H19" t="n" s="7">
+        <v>82010015</v>
+      </c>
+      <c r="I19" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J19" t="n" s="7">
+        <v>10703114</v>
+      </c>
+      <c r="K19" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7"/>
+      <c r="B20" t="n" s="7">
+        <v>92010016</v>
+      </c>
+      <c r="C20" t="str" s="7">
+        <v>玄罡撼岳劲·庚金真意</v>
+      </c>
+      <c r="D20" t="n" s="7">
+        <v>100400</v>
+      </c>
+      <c r="E20" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F20" t="n" s="7">
+        <v>10202003</v>
+      </c>
+      <c r="G20" t="str" s="3">
+        <v>玄罡撼岳劲：撼岳劲改为金行，保留击退。</v>
+      </c>
+      <c r="H20" t="n" s="7">
+        <v>82010016</v>
+      </c>
+      <c r="I20" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n" s="7">
+        <v>10703115</v>
+      </c>
+      <c r="K20" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7"/>
+      <c r="B21" t="n" s="7">
+        <v>92010017</v>
+      </c>
+      <c r="C21" t="str" s="7">
+        <v>玄罡撼岳劲·离火真意</v>
+      </c>
+      <c r="D21" t="n" s="7">
+        <v>100400</v>
+      </c>
+      <c r="E21" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F21" t="n" s="7">
+        <v>10202003</v>
+      </c>
+      <c r="G21" t="str" s="3">
+        <v>玄罡撼岳劲：撼岳劲改为火行，保留击退。</v>
+      </c>
+      <c r="H21" t="n" s="7">
+        <v>82010017</v>
+      </c>
+      <c r="I21" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n" s="7">
+        <v>10703116</v>
+      </c>
+      <c r="K21" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7"/>
+      <c r="B22" t="n" s="7">
+        <v>92010018</v>
+      </c>
+      <c r="C22" t="str" s="7">
+        <v>玄罡撼岳劲·长劲真意</v>
+      </c>
+      <c r="D22" t="n" s="7">
+        <v>100400</v>
+      </c>
+      <c r="E22" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F22" t="n" s="7">
+        <v>10202003</v>
+      </c>
+      <c r="G22" t="str" s="3">
+        <v>玄罡撼岳劲：贯穿劲气射程提高25%。</v>
+      </c>
+      <c r="H22" t="n" s="7">
+        <v>82010018</v>
+      </c>
+      <c r="I22" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J22" t="n" s="7">
+        <v>10703117</v>
+      </c>
+      <c r="K22" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7"/>
+      <c r="B23" t="n" s="7">
+        <v>92010019</v>
+      </c>
+      <c r="C23" t="str" s="7">
+        <v>玄罡撼岳劲·宽劲真意</v>
+      </c>
+      <c r="D23" t="n" s="7">
+        <v>100400</v>
+      </c>
+      <c r="E23" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F23" t="n" s="7">
+        <v>10202003</v>
+      </c>
+      <c r="G23" t="str" s="3">
+        <v>玄罡撼岳劲：劲气命中半径提高25%。</v>
+      </c>
+      <c r="H23" t="n" s="7">
+        <v>82010019</v>
+      </c>
+      <c r="I23" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J23" t="n" s="7">
+        <v>10703118</v>
+      </c>
+      <c r="K23" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7"/>
+      <c r="B24" t="n" s="7">
+        <v>92010020</v>
+      </c>
+      <c r="C24" t="str" s="7">
+        <v>玄罡撼岳劲·震退真意</v>
+      </c>
+      <c r="D24" t="n" s="7">
+        <v>100400</v>
+      </c>
+      <c r="E24" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F24" t="n" s="7">
+        <v>10202003</v>
+      </c>
+      <c r="G24" t="str" s="3">
+        <v>玄罡撼岳劲：命中后的击退距离提高25%。</v>
+      </c>
+      <c r="H24" t="n" s="7">
+        <v>82010020</v>
+      </c>
+      <c r="I24" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J24" t="n" s="7">
+        <v>10703119</v>
+      </c>
+      <c r="K24" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7"/>
+      <c r="B25" t="n" s="7">
+        <v>92010021</v>
+      </c>
+      <c r="C25" t="str" s="7">
+        <v>庚芒诀·离火真意</v>
+      </c>
+      <c r="D25" t="n" s="7">
+        <v>100500</v>
+      </c>
+      <c r="E25" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F25" t="n" s="7">
+        <v>10202004</v>
+      </c>
+      <c r="G25" t="str" s="3">
+        <v>庚芒诀：金芒改属火行，仍走法术伤害。</v>
+      </c>
+      <c r="H25" t="n" s="7">
+        <v>82010021</v>
+      </c>
+      <c r="I25" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n" s="7">
+        <v>10703120</v>
+      </c>
+      <c r="K25" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7"/>
+      <c r="B26" t="n" s="7">
+        <v>92010022</v>
+      </c>
+      <c r="C26" t="str" s="7">
+        <v>庚芒诀·玄水真意</v>
+      </c>
+      <c r="D26" t="n" s="7">
+        <v>100500</v>
+      </c>
+      <c r="E26" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F26" t="n" s="7">
+        <v>10202004</v>
+      </c>
+      <c r="G26" t="str" s="3">
+        <v>庚芒诀：金芒改属水行，仍走法术伤害。</v>
+      </c>
+      <c r="H26" t="n" s="7">
+        <v>82010022</v>
+      </c>
+      <c r="I26" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n" s="7">
+        <v>10703121</v>
+      </c>
+      <c r="K26" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7"/>
+      <c r="B27" t="n" s="7">
+        <v>92010023</v>
+      </c>
+      <c r="C27" t="str" s="7">
+        <v>庚芒诀·长虹真意</v>
+      </c>
+      <c r="D27" t="n" s="7">
+        <v>100500</v>
+      </c>
+      <c r="E27" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F27" t="n" s="7">
+        <v>10202004</v>
+      </c>
+      <c r="G27" t="str" s="3">
+        <v>庚芒诀：线形长度提高25%。</v>
+      </c>
+      <c r="H27" t="n" s="7">
+        <v>82010023</v>
+      </c>
+      <c r="I27" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J27" t="n" s="7">
+        <v>10703122</v>
+      </c>
+      <c r="K27" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7"/>
+      <c r="B28" t="n" s="7">
+        <v>92010024</v>
+      </c>
+      <c r="C28" t="str" s="7">
+        <v>庚芒诀·横芒真意</v>
+      </c>
+      <c r="D28" t="n" s="7">
+        <v>100500</v>
+      </c>
+      <c r="E28" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F28" t="n" s="7">
+        <v>10202004</v>
+      </c>
+      <c r="G28" t="str" s="3">
+        <v>庚芒诀：线形宽度提高30%。</v>
+      </c>
+      <c r="H28" t="n" s="7">
+        <v>82010024</v>
+      </c>
+      <c r="I28" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J28" t="n" s="7">
+        <v>10703123</v>
+      </c>
+      <c r="K28" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7"/>
+      <c r="B29" t="n" s="7">
+        <v>92010025</v>
+      </c>
+      <c r="C29" t="str" s="7">
+        <v>庚芒诀·锐贯真意</v>
+      </c>
+      <c r="D29" t="n" s="7">
+        <v>100500</v>
+      </c>
+      <c r="E29" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F29" t="n" s="7">
+        <v>10202004</v>
+      </c>
+      <c r="G29" t="str" s="3">
+        <v>庚芒诀：原伤害系数提高15%。</v>
+      </c>
+      <c r="H29" t="n" s="7">
+        <v>82010025</v>
+      </c>
+      <c r="I29" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J29" t="n" s="7">
+        <v>10703124</v>
+      </c>
+      <c r="K29" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7"/>
+      <c r="B30" t="n" s="7">
+        <v>92010026</v>
+      </c>
+      <c r="C30" t="str" s="7">
+        <v>青萝引·离火真意</v>
+      </c>
+      <c r="D30" t="n" s="7">
+        <v>100600</v>
+      </c>
+      <c r="E30" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F30" t="n" s="7">
+        <v>10202005</v>
+      </c>
+      <c r="G30" t="str" s="3">
+        <v>青萝引：藤刺改属火行，伤害通道不变。</v>
+      </c>
+      <c r="H30" t="n" s="7">
+        <v>82010026</v>
+      </c>
+      <c r="I30" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n" s="7">
+        <v>10703125</v>
+      </c>
+      <c r="K30" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7"/>
+      <c r="B31" t="n" s="7">
+        <v>92010027</v>
+      </c>
+      <c r="C31" t="str" s="7">
+        <v>青萝引·玄水真意</v>
+      </c>
+      <c r="D31" t="n" s="7">
+        <v>100600</v>
+      </c>
+      <c r="E31" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F31" t="n" s="7">
+        <v>10202005</v>
+      </c>
+      <c r="G31" t="str" s="3">
+        <v>青萝引：藤刺改属水行，伤害通道不变。</v>
+      </c>
+      <c r="H31" t="n" s="7">
+        <v>82010027</v>
+      </c>
+      <c r="I31" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n" s="7">
+        <v>10703126</v>
+      </c>
+      <c r="K31" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7"/>
+      <c r="B32" t="n" s="7">
+        <v>92010028</v>
+      </c>
+      <c r="C32" t="str" s="7">
+        <v>青萝引·繁萝真意</v>
+      </c>
+      <c r="D32" t="n" s="7">
+        <v>100600</v>
+      </c>
+      <c r="E32" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F32" t="n" s="7">
+        <v>10202005</v>
+      </c>
+      <c r="G32" t="str" s="3">
+        <v>青萝引：藤刺作用半径提高30%。</v>
+      </c>
+      <c r="H32" t="n" s="7">
+        <v>82010028</v>
+      </c>
+      <c r="I32" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J32" t="n" s="7">
+        <v>10703127</v>
+      </c>
+      <c r="K32" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7"/>
+      <c r="B33" t="n" s="7">
+        <v>92010029</v>
+      </c>
+      <c r="C33" t="str" s="7">
+        <v>青萝引·深刺真意</v>
+      </c>
+      <c r="D33" t="n" s="7">
+        <v>100600</v>
+      </c>
+      <c r="E33" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F33" t="n" s="7">
+        <v>10202005</v>
+      </c>
+      <c r="G33" t="str" s="3">
+        <v>青萝引：藤刺伤害系数提高15%。</v>
+      </c>
+      <c r="H33" t="n" s="7">
+        <v>82010029</v>
+      </c>
+      <c r="I33" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J33" t="n" s="7">
+        <v>10703128</v>
+      </c>
+      <c r="K33" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7"/>
+      <c r="B34" t="n" s="7">
+        <v>92010030</v>
+      </c>
+      <c r="C34" t="str" s="7">
+        <v>青萝引·遥引真意</v>
+      </c>
+      <c r="D34" t="n" s="7">
+        <v>100600</v>
+      </c>
+      <c r="E34" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F34" t="n" s="7">
+        <v>10202005</v>
+      </c>
+      <c r="G34" t="str" s="3">
+        <v>青萝引：施法距离提高20%。</v>
+      </c>
+      <c r="H34" t="n" s="7">
+        <v>82010030</v>
+      </c>
+      <c r="I34" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J34" t="n" s="7">
+        <v>10703129</v>
+      </c>
+      <c r="K34" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7"/>
+      <c r="B35" t="n" s="7">
+        <v>92010031</v>
+      </c>
+      <c r="C35" t="str" s="7">
+        <v>听潮印·庚金真意</v>
+      </c>
+      <c r="D35" t="n" s="7">
+        <v>100700</v>
+      </c>
+      <c r="E35" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F35" t="n" s="7">
+        <v>10202006</v>
+      </c>
+      <c r="G35" t="str" s="3">
+        <v>听潮印：潮印改属金行，伤害通道不变。</v>
+      </c>
+      <c r="H35" t="n" s="7">
+        <v>82010031</v>
+      </c>
+      <c r="I35" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n" s="7">
+        <v>10703130</v>
+      </c>
+      <c r="K35" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7"/>
+      <c r="B36" t="n" s="7">
+        <v>92010032</v>
+      </c>
+      <c r="C36" t="str" s="7">
+        <v>听潮印·青木真意</v>
+      </c>
+      <c r="D36" t="n" s="7">
+        <v>100700</v>
+      </c>
+      <c r="E36" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F36" t="n" s="7">
+        <v>10202006</v>
+      </c>
+      <c r="G36" t="str" s="3">
+        <v>听潮印：潮印改属木行，伤害通道不变。</v>
+      </c>
+      <c r="H36" t="n" s="7">
+        <v>82010032</v>
+      </c>
+      <c r="I36" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J36" t="n" s="7">
+        <v>10703131</v>
+      </c>
+      <c r="K36" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7"/>
+      <c r="B37" t="n" s="7">
+        <v>92010033</v>
+      </c>
+      <c r="C37" t="str" s="7">
+        <v>听潮印·涨潮真意</v>
+      </c>
+      <c r="D37" t="n" s="7">
+        <v>100700</v>
+      </c>
+      <c r="E37" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F37" t="n" s="7">
+        <v>10202006</v>
+      </c>
+      <c r="G37" t="str" s="3">
+        <v>听潮印：落点圆形半径提高25%。</v>
+      </c>
+      <c r="H37" t="n" s="7">
+        <v>82010033</v>
+      </c>
+      <c r="I37" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J37" t="n" s="7">
+        <v>10703132</v>
+      </c>
+      <c r="K37" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7"/>
+      <c r="B38" t="n" s="7">
+        <v>92010034</v>
+      </c>
+      <c r="C38" t="str" s="7">
+        <v>听潮印·叠浪真意</v>
+      </c>
+      <c r="D38" t="n" s="7">
+        <v>100700</v>
+      </c>
+      <c r="E38" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F38" t="n" s="7">
+        <v>10202006</v>
+      </c>
+      <c r="G38" t="str" s="3">
+        <v>听潮印：伤害系数提高15%。</v>
+      </c>
+      <c r="H38" t="n" s="7">
+        <v>82010034</v>
+      </c>
+      <c r="I38" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J38" t="n" s="7">
+        <v>10703133</v>
+      </c>
+      <c r="K38" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7"/>
+      <c r="B39" t="n" s="7">
+        <v>92010035</v>
+      </c>
+      <c r="C39" t="str" s="7">
+        <v>听潮印·潮回真意</v>
+      </c>
+      <c r="D39" t="n" s="7">
+        <v>100700</v>
+      </c>
+      <c r="E39" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F39" t="n" s="7">
+        <v>10202006</v>
+      </c>
+      <c r="G39" t="str" s="3">
+        <v>听潮印：冷却时间降低15%。</v>
+      </c>
+      <c r="H39" t="n" s="7">
+        <v>82010035</v>
+      </c>
+      <c r="I39" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J39" t="n" s="7">
+        <v>10703134</v>
+      </c>
+      <c r="K39" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7"/>
+      <c r="B40" t="n" s="7">
+        <v>92010036</v>
+      </c>
+      <c r="C40" t="str" s="7">
+        <v>离火星·庚金真意</v>
+      </c>
+      <c r="D40" t="n" s="7">
+        <v>100800</v>
+      </c>
+      <c r="E40" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F40" t="n" s="7">
+        <v>10202007</v>
+      </c>
+      <c r="G40" t="str" s="3">
+        <v>离火星：火球改属金行，仍走法术伤害。</v>
+      </c>
+      <c r="H40" t="n" s="7">
+        <v>82010036</v>
+      </c>
+      <c r="I40" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J40" t="n" s="7">
+        <v>10703135</v>
+      </c>
+      <c r="K40" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7"/>
+      <c r="B41" t="n" s="7">
+        <v>92010037</v>
+      </c>
+      <c r="C41" t="str" s="7">
+        <v>离火星·玄水真意</v>
+      </c>
+      <c r="D41" t="n" s="7">
+        <v>100800</v>
+      </c>
+      <c r="E41" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F41" t="n" s="7">
+        <v>10202007</v>
+      </c>
+      <c r="G41" t="str" s="3">
+        <v>离火星：火球改属水行，仍走法术伤害。</v>
+      </c>
+      <c r="H41" t="n" s="7">
+        <v>82010037</v>
+      </c>
+      <c r="I41" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J41" t="n" s="7">
+        <v>10703136</v>
+      </c>
+      <c r="K41" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7"/>
+      <c r="B42" t="n" s="7">
+        <v>92010038</v>
+      </c>
+      <c r="C42" t="str" s="7">
+        <v>离火星·双星真意</v>
+      </c>
+      <c r="D42" t="n" s="7">
+        <v>100800</v>
+      </c>
+      <c r="E42" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F42" t="n" s="7">
+        <v>10202007</v>
+      </c>
+      <c r="G42" t="str" s="3">
+        <v>离火星：同一次施放发出两枚火球，沿原方向连续出射。</v>
+      </c>
+      <c r="H42" t="n" s="7">
+        <v>82010038</v>
+      </c>
+      <c r="I42" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J42" t="n" s="7">
+        <v>10703137</v>
+      </c>
+      <c r="K42" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7"/>
+      <c r="B43" t="n" s="7">
+        <v>92010039</v>
+      </c>
+      <c r="C43" t="str" s="7">
+        <v>离火星·流星真意</v>
+      </c>
+      <c r="D43" t="n" s="7">
+        <v>100800</v>
+      </c>
+      <c r="E43" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F43" t="n" s="7">
+        <v>10202007</v>
+      </c>
+      <c r="G43" t="str" s="3">
+        <v>离火星：火球飞行速度提高30%。</v>
+      </c>
+      <c r="H43" t="n" s="7">
+        <v>82010039</v>
+      </c>
+      <c r="I43" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J43" t="n" s="7">
+        <v>10703138</v>
+      </c>
+      <c r="K43" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7"/>
+      <c r="B44" t="n" s="7">
+        <v>92010040</v>
+      </c>
+      <c r="C44" t="str" s="7">
+        <v>离火星·穿焰真意</v>
+      </c>
+      <c r="D44" t="n" s="7">
+        <v>100800</v>
+      </c>
+      <c r="E44" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F44" t="n" s="7">
+        <v>10202007</v>
+      </c>
+      <c r="G44" t="str" s="3">
+        <v>离火星：火球还可穿过一个目标。</v>
+      </c>
+      <c r="H44" t="n" s="7">
+        <v>82010040</v>
+      </c>
+      <c r="I44" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J44" t="n" s="7">
+        <v>10703139</v>
+      </c>
+      <c r="K44" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7"/>
+      <c r="B45" t="n" s="7">
+        <v>92010041</v>
+      </c>
+      <c r="C45" t="str" s="7">
+        <v>凝岳印·庚金真意</v>
+      </c>
+      <c r="D45" t="n" s="7">
+        <v>100900</v>
+      </c>
+      <c r="E45" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F45" t="n" s="7">
+        <v>10202008</v>
+      </c>
+      <c r="G45" t="str" s="3">
+        <v>凝岳印：土印改属金行，伤害通道不变。</v>
+      </c>
+      <c r="H45" t="n" s="7">
+        <v>82010041</v>
+      </c>
+      <c r="I45" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J45" t="n" s="7">
+        <v>10703140</v>
+      </c>
+      <c r="K45" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7"/>
+      <c r="B46" t="n" s="7">
+        <v>92010042</v>
+      </c>
+      <c r="C46" t="str" s="7">
+        <v>凝岳印·离火真意</v>
+      </c>
+      <c r="D46" t="n" s="7">
+        <v>100900</v>
+      </c>
+      <c r="E46" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F46" t="n" s="7">
+        <v>10202008</v>
+      </c>
+      <c r="G46" t="str" s="3">
+        <v>凝岳印：土印改属火行，伤害通道不变。</v>
+      </c>
+      <c r="H46" t="n" s="7">
+        <v>82010042</v>
+      </c>
+      <c r="I46" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J46" t="n" s="7">
+        <v>10703141</v>
+      </c>
+      <c r="K46" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7"/>
+      <c r="B47" t="n" s="7">
+        <v>92010043</v>
+      </c>
+      <c r="C47" t="str" s="7">
+        <v>凝岳印·速坠真意</v>
+      </c>
+      <c r="D47" t="n" s="7">
+        <v>100900</v>
+      </c>
+      <c r="E47" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F47" t="n" s="7">
+        <v>10202008</v>
+      </c>
+      <c r="G47" t="str" s="3">
+        <v>凝岳印：落印等待由5000毫秒改为3500毫秒。</v>
+      </c>
+      <c r="H47" t="n" s="7">
+        <v>82010043</v>
+      </c>
+      <c r="I47" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J47" t="n" s="7">
+        <v>10703142</v>
+      </c>
+      <c r="K47" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7"/>
+      <c r="B48" t="n" s="7">
+        <v>92010044</v>
+      </c>
+      <c r="C48" t="str" s="7">
+        <v>凝岳印·遥印真意</v>
+      </c>
+      <c r="D48" t="n" s="7">
+        <v>100900</v>
+      </c>
+      <c r="E48" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F48" t="n" s="7">
+        <v>10202008</v>
+      </c>
+      <c r="G48" t="str" s="3">
+        <v>凝岳印：施法距离提高20%。</v>
+      </c>
+      <c r="H48" t="n" s="7">
+        <v>82010044</v>
+      </c>
+      <c r="I48" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J48" t="n" s="7">
+        <v>10703143</v>
+      </c>
+      <c r="K48" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7"/>
+      <c r="B49" t="n" s="7">
+        <v>92010045</v>
+      </c>
+      <c r="C49" t="str" s="7">
+        <v>凝岳印·广印真意</v>
+      </c>
+      <c r="D49" t="n" s="7">
+        <v>100900</v>
+      </c>
+      <c r="E49" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F49" t="n" s="7">
+        <v>10202008</v>
+      </c>
+      <c r="G49" t="str" s="3">
+        <v>凝岳印：落地爆发范围提高25%。</v>
+      </c>
+      <c r="H49" t="n" s="7">
+        <v>82010045</v>
+      </c>
+      <c r="I49" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J49" t="n" s="7">
+        <v>10703144</v>
+      </c>
+      <c r="K49" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7"/>
+      <c r="B50" t="n" s="7">
+        <v>92010046</v>
+      </c>
+      <c r="C50" t="str" s="7">
+        <v>惊蛰落霆·庚金真意</v>
+      </c>
+      <c r="D50" t="n" s="7">
+        <v>101000</v>
+      </c>
+      <c r="E50" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F50" t="n" s="7">
+        <v>10202009</v>
+      </c>
+      <c r="G50" t="str" s="3">
+        <v>惊蛰落霆：落雷改属金行，仍走法术伤害。</v>
+      </c>
+      <c r="H50" t="n" s="7">
+        <v>82010046</v>
+      </c>
+      <c r="I50" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J50" t="n" s="7">
+        <v>10703145</v>
+      </c>
+      <c r="K50" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7"/>
+      <c r="B51" t="n" s="7">
+        <v>92010047</v>
+      </c>
+      <c r="C51" t="str" s="7">
+        <v>惊蛰落霆·离火真意</v>
+      </c>
+      <c r="D51" t="n" s="7">
+        <v>101000</v>
+      </c>
+      <c r="E51" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F51" t="n" s="7">
+        <v>10202009</v>
+      </c>
+      <c r="G51" t="str" s="3">
+        <v>惊蛰落霆：落雷改属火行，仍走法术伤害。</v>
+      </c>
+      <c r="H51" t="n" s="7">
+        <v>82010047</v>
+      </c>
+      <c r="I51" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J51" t="n" s="7">
+        <v>10703146</v>
+      </c>
+      <c r="K51" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7"/>
+      <c r="B52" t="n" s="7">
+        <v>92010048</v>
+      </c>
+      <c r="C52" t="str" s="7">
+        <v>惊蛰落霆·雷域真意</v>
+      </c>
+      <c r="D52" t="n" s="7">
+        <v>101000</v>
+      </c>
+      <c r="E52" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F52" t="n" s="7">
+        <v>10202009</v>
+      </c>
+      <c r="G52" t="str" s="3">
+        <v>惊蛰落霆：落雷半径提高25%。</v>
+      </c>
+      <c r="H52" t="n" s="7">
+        <v>82010048</v>
+      </c>
+      <c r="I52" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J52" t="n" s="7">
+        <v>10703147</v>
+      </c>
+      <c r="K52" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7"/>
+      <c r="B53" t="n" s="7">
+        <v>92010049</v>
+      </c>
+      <c r="C53" t="str" s="7">
+        <v>惊蛰落霆·雷威真意</v>
+      </c>
+      <c r="D53" t="n" s="7">
+        <v>101000</v>
+      </c>
+      <c r="E53" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F53" t="n" s="7">
+        <v>10202009</v>
+      </c>
+      <c r="G53" t="str" s="3">
+        <v>惊蛰落霆：伤害系数提高15%。</v>
+      </c>
+      <c r="H53" t="n" s="7">
+        <v>82010049</v>
+      </c>
+      <c r="I53" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J53" t="n" s="7">
+        <v>10703148</v>
+      </c>
+      <c r="K53" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7"/>
+      <c r="B54" t="n" s="7">
+        <v>92010050</v>
+      </c>
+      <c r="C54" t="str" s="7">
+        <v>惊蛰落霆·惊雷真意</v>
+      </c>
+      <c r="D54" t="n" s="7">
+        <v>101000</v>
+      </c>
+      <c r="E54" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F54" t="n" s="7">
+        <v>10202009</v>
+      </c>
+      <c r="G54" t="str" s="3">
+        <v>惊蛰落霆：额外增加5个百分点技能暴击率。</v>
+      </c>
+      <c r="H54" t="n" s="7">
+        <v>82010050</v>
+      </c>
+      <c r="I54" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J54" t="n" s="7">
+        <v>10703149</v>
+      </c>
+      <c r="K54" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7"/>
+      <c r="B55" t="n" s="7">
+        <v>92010051</v>
+      </c>
+      <c r="C55" t="str" s="7">
+        <v>赤霄焚野·青木真意</v>
+      </c>
+      <c r="D55" t="n" s="7">
+        <v>101100</v>
+      </c>
+      <c r="E55" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F55" t="n" s="7">
+        <v>10202010</v>
+      </c>
+      <c r="G55" t="str" s="3">
+        <v>赤霄焚野：火纹改属木行，保留两段释放。</v>
+      </c>
+      <c r="H55" t="n" s="7">
+        <v>82010051</v>
+      </c>
+      <c r="I55" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J55" t="n" s="7">
+        <v>10703150</v>
+      </c>
+      <c r="K55" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7"/>
+      <c r="B56" t="n" s="7">
+        <v>92010052</v>
+      </c>
+      <c r="C56" t="str" s="7">
+        <v>赤霄焚野·玄水真意</v>
+      </c>
+      <c r="D56" t="n" s="7">
+        <v>101100</v>
+      </c>
+      <c r="E56" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F56" t="n" s="7">
+        <v>10202010</v>
+      </c>
+      <c r="G56" t="str" s="3">
+        <v>赤霄焚野：火纹改属水行，保留两段释放。</v>
+      </c>
+      <c r="H56" t="n" s="7">
+        <v>82010052</v>
+      </c>
+      <c r="I56" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J56" t="n" s="7">
+        <v>10703151</v>
+      </c>
+      <c r="K56" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7"/>
+      <c r="B57" t="n" s="7">
+        <v>92010053</v>
+      </c>
+      <c r="C57" t="str" s="7">
+        <v>赤霄焚野·急焚真意</v>
+      </c>
+      <c r="D57" t="n" s="7">
+        <v>101100</v>
+      </c>
+      <c r="E57" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F57" t="n" s="7">
+        <v>10202010</v>
+      </c>
+      <c r="G57" t="str" s="3">
+        <v>赤霄焚野：第二段释放由2000毫秒提前到1000毫秒。</v>
+      </c>
+      <c r="H57" t="n" s="7">
+        <v>82010053</v>
+      </c>
+      <c r="I57" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J57" t="n" s="7">
+        <v>10703152</v>
+      </c>
+      <c r="K57" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7"/>
+      <c r="B58" t="n" s="7">
+        <v>92010054</v>
+      </c>
+      <c r="C58" t="str" s="7">
+        <v>赤霄焚野·遥焚真意</v>
+      </c>
+      <c r="D58" t="n" s="7">
+        <v>101100</v>
+      </c>
+      <c r="E58" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F58" t="n" s="7">
+        <v>10202010</v>
+      </c>
+      <c r="G58" t="str" s="3">
+        <v>赤霄焚野：施法距离提高20%。</v>
+      </c>
+      <c r="H58" t="n" s="7">
+        <v>82010054</v>
+      </c>
+      <c r="I58" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J58" t="n" s="7">
+        <v>10703153</v>
+      </c>
+      <c r="K58" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7"/>
+      <c r="B59" t="n" s="7">
+        <v>92010055</v>
+      </c>
+      <c r="C59" t="str" s="7">
+        <v>赤霄焚野·回焰真意</v>
+      </c>
+      <c r="D59" t="n" s="7">
+        <v>101100</v>
+      </c>
+      <c r="E59" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F59" t="n" s="7">
+        <v>10202010</v>
+      </c>
+      <c r="G59" t="str" s="3">
+        <v>赤霄焚野：冷却时间降低15%。</v>
+      </c>
+      <c r="H59" t="n" s="7">
+        <v>82010055</v>
+      </c>
+      <c r="I59" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J59" t="n" s="7">
+        <v>10703154</v>
+      </c>
+      <c r="K59" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7"/>
+      <c r="B60" t="n" s="7">
+        <v>92010056</v>
+      </c>
+      <c r="C60" t="str" s="7">
+        <v>御锋诀·庚金真意</v>
+      </c>
+      <c r="D60" t="n" s="7">
+        <v>101200</v>
+      </c>
+      <c r="E60" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F60" t="n" s="7">
+        <v>10202011</v>
+      </c>
+      <c r="G60" t="str" s="3">
+        <v>御锋诀：飞剑改属金行，物理伤害通道不变。</v>
+      </c>
+      <c r="H60" t="n" s="7">
+        <v>82010056</v>
+      </c>
+      <c r="I60" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J60" t="n" s="7">
+        <v>10703155</v>
+      </c>
+      <c r="K60" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7"/>
+      <c r="B61" t="n" s="7">
+        <v>92010057</v>
+      </c>
+      <c r="C61" t="str" s="7">
+        <v>御锋诀·离火真意</v>
+      </c>
+      <c r="D61" t="n" s="7">
+        <v>101200</v>
+      </c>
+      <c r="E61" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F61" t="n" s="7">
+        <v>10202011</v>
+      </c>
+      <c r="G61" t="str" s="3">
+        <v>御锋诀：飞剑改属火行，物理伤害通道不变。</v>
+      </c>
+      <c r="H61" t="n" s="7">
+        <v>82010057</v>
+      </c>
+      <c r="I61" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J61" t="n" s="7">
+        <v>10703156</v>
+      </c>
+      <c r="K61" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7"/>
+      <c r="B62" t="n" s="7">
+        <v>92010058</v>
+      </c>
+      <c r="C62" t="str" s="7">
+        <v>御锋诀·双御真意</v>
+      </c>
+      <c r="D62" t="n" s="7">
+        <v>101200</v>
+      </c>
+      <c r="E62" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F62" t="n" s="7">
+        <v>10202011</v>
+      </c>
+      <c r="G62" t="str" s="3">
+        <v>御锋诀：一次施法连续御出两剑。</v>
+      </c>
+      <c r="H62" t="n" s="7">
+        <v>82010058</v>
+      </c>
+      <c r="I62" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J62" t="n" s="7">
+        <v>10703157</v>
+      </c>
+      <c r="K62" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7"/>
+      <c r="B63" t="n" s="7">
+        <v>92010059</v>
+      </c>
+      <c r="C63" t="str" s="7">
+        <v>御锋诀·疾御真意</v>
+      </c>
+      <c r="D63" t="n" s="7">
+        <v>101200</v>
+      </c>
+      <c r="E63" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F63" t="n" s="7">
+        <v>10202011</v>
+      </c>
+      <c r="G63" t="str" s="3">
+        <v>御锋诀：飞剑速度提高30%。</v>
+      </c>
+      <c r="H63" t="n" s="7">
+        <v>82010059</v>
+      </c>
+      <c r="I63" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J63" t="n" s="7">
+        <v>10703158</v>
+      </c>
+      <c r="K63" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7"/>
+      <c r="B64" t="n" s="7">
+        <v>92010060</v>
+      </c>
+      <c r="C64" t="str" s="7">
+        <v>御锋诀·远御真意</v>
+      </c>
+      <c r="D64" t="n" s="7">
+        <v>101200</v>
+      </c>
+      <c r="E64" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F64" t="n" s="7">
+        <v>10202011</v>
+      </c>
+      <c r="G64" t="str" s="3">
+        <v>御锋诀：施法距离与弹道射程均提高20%。</v>
+      </c>
+      <c r="H64" t="n" s="7">
+        <v>82010060</v>
+      </c>
+      <c r="I64" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J64" t="n" s="7">
+        <v>10703159</v>
+      </c>
+      <c r="K64" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7"/>
+      <c r="B65" t="n" s="7">
+        <v>92010061</v>
+      </c>
+      <c r="C65" t="str" s="7">
+        <v>分光剑诀·庚金真意</v>
+      </c>
+      <c r="D65" t="n" s="7">
+        <v>101300</v>
+      </c>
+      <c r="E65" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F65" t="n" s="7">
+        <v>10202012</v>
+      </c>
+      <c r="G65" t="str" s="3">
+        <v>分光剑诀：分光剑影改属金行，物理通道不变。</v>
+      </c>
+      <c r="H65" t="n" s="7">
+        <v>82010061</v>
+      </c>
+      <c r="I65" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J65" t="n" s="7">
+        <v>10703160</v>
+      </c>
+      <c r="K65" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7"/>
+      <c r="B66" t="n" s="7">
+        <v>92010062</v>
+      </c>
+      <c r="C66" t="str" s="7">
+        <v>分光剑诀·离火真意</v>
+      </c>
+      <c r="D66" t="n" s="7">
+        <v>101300</v>
+      </c>
+      <c r="E66" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F66" t="n" s="7">
+        <v>10202012</v>
+      </c>
+      <c r="G66" t="str" s="3">
+        <v>分光剑诀：分光剑影改属火行，物理通道不变。</v>
+      </c>
+      <c r="H66" t="n" s="7">
+        <v>82010062</v>
+      </c>
+      <c r="I66" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J66" t="n" s="7">
+        <v>10703161</v>
+      </c>
+      <c r="K66" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7"/>
+      <c r="B67" t="n" s="7">
+        <v>92010063</v>
+      </c>
+      <c r="C67" t="str" s="7">
+        <v>分光剑诀·疾影真意</v>
+      </c>
+      <c r="D67" t="n" s="7">
+        <v>101300</v>
+      </c>
+      <c r="E67" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F67" t="n" s="7">
+        <v>10202012</v>
+      </c>
+      <c r="G67" t="str" s="3">
+        <v>分光剑诀：首枚飞剑速度提高30%。</v>
+      </c>
+      <c r="H67" t="n" s="7">
+        <v>82010063</v>
+      </c>
+      <c r="I67" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J67" t="n" s="7">
+        <v>10703162</v>
+      </c>
+      <c r="K67" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7"/>
+      <c r="B68" t="n" s="7">
+        <v>92010064</v>
+      </c>
+      <c r="C68" t="str" s="7">
+        <v>分光剑诀·远影真意</v>
+      </c>
+      <c r="D68" t="n" s="7">
+        <v>101300</v>
+      </c>
+      <c r="E68" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F68" t="n" s="7">
+        <v>10202012</v>
+      </c>
+      <c r="G68" t="str" s="3">
+        <v>分光剑诀：飞剑射程提高20%。</v>
+      </c>
+      <c r="H68" t="n" s="7">
+        <v>82010064</v>
+      </c>
+      <c r="I68" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J68" t="n" s="7">
+        <v>10703163</v>
+      </c>
+      <c r="K68" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7"/>
+      <c r="B69" t="n" s="7">
+        <v>92010065</v>
+      </c>
+      <c r="C69" t="str" s="7">
+        <v>分光剑诀·回光真意</v>
+      </c>
+      <c r="D69" t="n" s="7">
+        <v>101300</v>
+      </c>
+      <c r="E69" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F69" t="n" s="7">
+        <v>10202012</v>
+      </c>
+      <c r="G69" t="str" s="3">
+        <v>分光剑诀：冷却时间降低15%。</v>
+      </c>
+      <c r="H69" t="n" s="7">
+        <v>82010065</v>
+      </c>
+      <c r="I69" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J69" t="n" s="7">
+        <v>10703164</v>
+      </c>
+      <c r="K69" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7"/>
+      <c r="B70" t="n" s="7">
+        <v>92010066</v>
+      </c>
+      <c r="C70" t="str" s="7">
+        <v>周天游刃·庚金真意</v>
+      </c>
+      <c r="D70" t="n" s="7">
+        <v>101400</v>
+      </c>
+      <c r="E70" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F70" t="n" s="7">
+        <v>10202013</v>
+      </c>
+      <c r="G70" t="str" s="3">
+        <v>周天游刃：十六飞剑改属金行，物理通道不变。</v>
+      </c>
+      <c r="H70" t="n" s="7">
+        <v>82010066</v>
+      </c>
+      <c r="I70" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J70" t="n" s="7">
+        <v>10703165</v>
+      </c>
+      <c r="K70" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7"/>
+      <c r="B71" t="n" s="7">
+        <v>92010067</v>
+      </c>
+      <c r="C71" t="str" s="7">
+        <v>周天游刃·离火真意</v>
+      </c>
+      <c r="D71" t="n" s="7">
+        <v>101400</v>
+      </c>
+      <c r="E71" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F71" t="n" s="7">
+        <v>10202013</v>
+      </c>
+      <c r="G71" t="str" s="3">
+        <v>周天游刃：十六飞剑改属火行，物理通道不变。</v>
+      </c>
+      <c r="H71" t="n" s="7">
+        <v>82010067</v>
+      </c>
+      <c r="I71" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J71" t="n" s="7">
+        <v>10703166</v>
+      </c>
+      <c r="K71" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7"/>
+      <c r="B72" t="n" s="7">
+        <v>92010068</v>
+      </c>
+      <c r="C72" t="str" s="7">
+        <v>周天游刃·添刃真意</v>
+      </c>
+      <c r="D72" t="n" s="7">
+        <v>101400</v>
+      </c>
+      <c r="E72" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F72" t="n" s="7">
+        <v>10202013</v>
+      </c>
+      <c r="G72" t="str" s="3">
+        <v>周天游刃：飞剑总数由16柄增加至18柄。</v>
+      </c>
+      <c r="H72" t="n" s="7">
+        <v>82010068</v>
+      </c>
+      <c r="I72" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J72" t="n" s="7">
+        <v>10703167</v>
+      </c>
+      <c r="K72" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7"/>
+      <c r="B73" t="n" s="7">
+        <v>92010069</v>
+      </c>
+      <c r="C73" t="str" s="7">
+        <v>周天游刃·急御真意</v>
+      </c>
+      <c r="D73" t="n" s="7">
+        <v>101400</v>
+      </c>
+      <c r="E73" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F73" t="n" s="7">
+        <v>10202013</v>
+      </c>
+      <c r="G73" t="str" s="3">
+        <v>周天游刃：发射波次间隔由100毫秒缩短为80毫秒。</v>
+      </c>
+      <c r="H73" t="n" s="7">
+        <v>82010069</v>
+      </c>
+      <c r="I73" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J73" t="n" s="7">
+        <v>10703168</v>
+      </c>
+      <c r="K73" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7"/>
+      <c r="B74" t="n" s="7">
+        <v>92010070</v>
+      </c>
+      <c r="C74" t="str" s="7">
+        <v>周天游刃·远游真意</v>
+      </c>
+      <c r="D74" t="n" s="7">
+        <v>101400</v>
+      </c>
+      <c r="E74" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F74" t="n" s="7">
+        <v>10202013</v>
+      </c>
+      <c r="G74" t="str" s="3">
+        <v>周天游刃：弹道射程提高20%。</v>
+      </c>
+      <c r="H74" t="n" s="7">
+        <v>82010070</v>
+      </c>
+      <c r="I74" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J74" t="n" s="7">
+        <v>10703169</v>
+      </c>
+      <c r="K74" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7"/>
+      <c r="B75" t="n" s="7">
+        <v>92010071</v>
+      </c>
+      <c r="C75" t="str" s="7">
+        <v>星罗分锋·庚金真意</v>
+      </c>
+      <c r="D75" t="n" s="7">
+        <v>101500</v>
+      </c>
+      <c r="E75" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F75" t="n" s="7">
+        <v>10202014</v>
+      </c>
+      <c r="G75" t="str" s="3">
+        <v>星罗分锋：散射剑阵改属金行，物理通道不变。</v>
+      </c>
+      <c r="H75" t="n" s="7">
+        <v>82010071</v>
+      </c>
+      <c r="I75" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n" s="7">
+        <v>10703170</v>
+      </c>
+      <c r="K75" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7"/>
+      <c r="B76" t="n" s="7">
+        <v>92010072</v>
+      </c>
+      <c r="C76" t="str" s="7">
+        <v>星罗分锋·离火真意</v>
+      </c>
+      <c r="D76" t="n" s="7">
+        <v>101500</v>
+      </c>
+      <c r="E76" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F76" t="n" s="7">
+        <v>10202014</v>
+      </c>
+      <c r="G76" t="str" s="3">
+        <v>星罗分锋：散射剑阵改属火行，物理通道不变。</v>
+      </c>
+      <c r="H76" t="n" s="7">
+        <v>82010072</v>
+      </c>
+      <c r="I76" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J76" t="n" s="7">
+        <v>10703171</v>
+      </c>
+      <c r="K76" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7"/>
+      <c r="B77" t="n" s="7">
+        <v>92010073</v>
+      </c>
+      <c r="C77" t="str" s="7">
+        <v>星罗分锋·密锋真意</v>
+      </c>
+      <c r="D77" t="n" s="7">
+        <v>101500</v>
+      </c>
+      <c r="E77" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F77" t="n" s="7">
+        <v>10202014</v>
+      </c>
+      <c r="G77" t="str" s="3">
+        <v>星罗分锋：第二段剑阵由800毫秒提前至400毫秒。</v>
+      </c>
+      <c r="H77" t="n" s="7">
+        <v>82010073</v>
+      </c>
+      <c r="I77" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J77" t="n" s="7">
+        <v>10703172</v>
+      </c>
+      <c r="K77" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7"/>
+      <c r="B78" t="n" s="7">
+        <v>92010074</v>
+      </c>
+      <c r="C78" t="str" s="7">
+        <v>星罗分锋·疾锋真意</v>
+      </c>
+      <c r="D78" t="n" s="7">
+        <v>101500</v>
+      </c>
+      <c r="E78" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F78" t="n" s="7">
+        <v>10202014</v>
+      </c>
+      <c r="G78" t="str" s="3">
+        <v>星罗分锋：冷却时间降低15%。</v>
+      </c>
+      <c r="H78" t="n" s="7">
+        <v>82010074</v>
+      </c>
+      <c r="I78" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J78" t="n" s="7">
+        <v>10703173</v>
+      </c>
+      <c r="K78" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7"/>
+      <c r="B79" t="n" s="7">
+        <v>92010075</v>
+      </c>
+      <c r="C79" t="str" s="7">
+        <v>星罗分锋·蓄锋真意</v>
+      </c>
+      <c r="D79" t="n" s="7">
+        <v>101500</v>
+      </c>
+      <c r="E79" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F79" t="n" s="7">
+        <v>10202014</v>
+      </c>
+      <c r="G79" t="str" s="3">
+        <v>星罗分锋：可储存两次释放，单层恢复12000毫秒；以较慢的长期恢复换取两次爆发。</v>
+      </c>
+      <c r="H79" t="n" s="7">
+        <v>82010075</v>
+      </c>
+      <c r="I79" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J79" t="n" s="7">
+        <v>10703174</v>
+      </c>
+      <c r="K79" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7"/>
+      <c r="B80" t="n" s="7">
+        <v>92010076</v>
+      </c>
+      <c r="C80" t="str" s="7">
+        <v>青息回元·群息真意</v>
+      </c>
+      <c r="D80" t="n" s="7">
+        <v>101600</v>
+      </c>
+      <c r="E80" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F80" t="n" s="7">
+        <v>10202015</v>
+      </c>
+      <c r="G80" t="str" s="3">
+        <v>青息回元：从单体治疗改为落点小范围治疗，最多治疗3名友方。</v>
+      </c>
+      <c r="H80" t="n" s="7">
+        <v>82010076</v>
+      </c>
+      <c r="I80" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J80" t="n" s="7">
+        <v>10703175</v>
+      </c>
+      <c r="K80" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7"/>
+      <c r="B81" t="n" s="7">
+        <v>92010077</v>
+      </c>
+      <c r="C81" t="str" s="7">
+        <v>青息回元·护元真意</v>
+      </c>
+      <c r="D81" t="n" s="7">
+        <v>101600</v>
+      </c>
+      <c r="E81" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F81" t="n" s="7">
+        <v>10202015</v>
+      </c>
+      <c r="G81" t="str" s="3">
+        <v>青息回元：治疗同时给目标附加短时小护盾。</v>
+      </c>
+      <c r="H81" t="n" s="7">
+        <v>82010077</v>
+      </c>
+      <c r="I81" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J81" t="n" s="7">
+        <v>10703176</v>
+      </c>
+      <c r="K81" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7"/>
+      <c r="B82" t="n" s="7">
+        <v>92010078</v>
+      </c>
+      <c r="C82" t="str" s="7">
+        <v>青息回元·浓息真意</v>
+      </c>
+      <c r="D82" t="n" s="7">
+        <v>101600</v>
+      </c>
+      <c r="E82" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F82" t="n" s="7">
+        <v>10202015</v>
+      </c>
+      <c r="G82" t="str" s="3">
+        <v>青息回元：治疗系数提高20%。</v>
+      </c>
+      <c r="H82" t="n" s="7">
+        <v>82010078</v>
+      </c>
+      <c r="I82" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J82" t="n" s="7">
+        <v>10703177</v>
+      </c>
+      <c r="K82" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="7"/>
+      <c r="B83" t="n" s="7">
+        <v>92010079</v>
+      </c>
+      <c r="C83" t="str" s="7">
+        <v>青息回元·遥息真意</v>
+      </c>
+      <c r="D83" t="n" s="7">
+        <v>101600</v>
+      </c>
+      <c r="E83" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F83" t="n" s="7">
+        <v>10202015</v>
+      </c>
+      <c r="G83" t="str" s="3">
+        <v>青息回元：治疗施法距离提高20%。</v>
+      </c>
+      <c r="H83" t="n" s="7">
+        <v>82010079</v>
+      </c>
+      <c r="I83" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J83" t="n" s="7">
+        <v>10703178</v>
+      </c>
+      <c r="K83" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7"/>
+      <c r="B84" t="n" s="7">
+        <v>92010080</v>
+      </c>
+      <c r="C84" t="str" s="7">
+        <v>青息回元·回息真意</v>
+      </c>
+      <c r="D84" t="n" s="7">
+        <v>101600</v>
+      </c>
+      <c r="E84" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F84" t="n" s="7">
+        <v>10202015</v>
+      </c>
+      <c r="G84" t="str" s="3">
+        <v>青息回元：冷却时间降低15%。</v>
+      </c>
+      <c r="H84" t="n" s="7">
+        <v>82010080</v>
+      </c>
+      <c r="I84" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J84" t="n" s="7">
+        <v>10703179</v>
+      </c>
+      <c r="K84" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="7"/>
+      <c r="B85" t="n" s="7">
+        <v>92010081</v>
+      </c>
+      <c r="C85" t="str" s="7">
+        <v>春脉绵生·延春真意</v>
+      </c>
+      <c r="D85" t="n" s="7">
+        <v>101700</v>
+      </c>
+      <c r="E85" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F85" t="n" s="7">
+        <v>10202016</v>
+      </c>
+      <c r="G85" t="str" s="3">
+        <v>春脉绵生：持续治疗状态的时长提高25%。</v>
+      </c>
+      <c r="H85" t="n" s="7">
+        <v>82010081</v>
+      </c>
+      <c r="I85" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J85" t="n" s="7">
+        <v>10703180</v>
+      </c>
+      <c r="K85" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="7"/>
+      <c r="B86" t="n" s="7">
+        <v>92010082</v>
+      </c>
+      <c r="C86" t="str" s="7">
+        <v>春脉绵生·密春真意</v>
+      </c>
+      <c r="D86" t="n" s="7">
+        <v>101700</v>
+      </c>
+      <c r="E86" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F86" t="n" s="7">
+        <v>10202016</v>
+      </c>
+      <c r="G86" t="str" s="3">
+        <v>春脉绵生：持续治疗间隔降低20%，每跳治疗不变。</v>
+      </c>
+      <c r="H86" t="n" s="7">
+        <v>82010082</v>
+      </c>
+      <c r="I86" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J86" t="n" s="7">
+        <v>10703181</v>
+      </c>
+      <c r="K86" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="7"/>
+      <c r="B87" t="n" s="7">
+        <v>92010083</v>
+      </c>
+      <c r="C87" t="str" s="7">
+        <v>春脉绵生·润脉真意</v>
+      </c>
+      <c r="D87" t="n" s="7">
+        <v>101700</v>
+      </c>
+      <c r="E87" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F87" t="n" s="7">
+        <v>10202016</v>
+      </c>
+      <c r="G87" t="str" s="3">
+        <v>春脉绵生：每跳治疗系数提高15%。</v>
+      </c>
+      <c r="H87" t="n" s="7">
+        <v>82010083</v>
+      </c>
+      <c r="I87" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J87" t="n" s="7">
+        <v>10703182</v>
+      </c>
+      <c r="K87" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="7"/>
+      <c r="B88" t="n" s="7">
+        <v>92010084</v>
+      </c>
+      <c r="C88" t="str" s="7">
+        <v>春脉绵生·遥春真意</v>
+      </c>
+      <c r="D88" t="n" s="7">
+        <v>101700</v>
+      </c>
+      <c r="E88" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F88" t="n" s="7">
+        <v>10202016</v>
+      </c>
+      <c r="G88" t="str" s="3">
+        <v>春脉绵生：施法距离提高20%。</v>
+      </c>
+      <c r="H88" t="n" s="7">
+        <v>82010084</v>
+      </c>
+      <c r="I88" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J88" t="n" s="7">
+        <v>10703183</v>
+      </c>
+      <c r="K88" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7"/>
+      <c r="B89" t="n" s="7">
+        <v>92010085</v>
+      </c>
+      <c r="C89" t="str" s="7">
+        <v>春脉绵生·春回真意</v>
+      </c>
+      <c r="D89" t="n" s="7">
+        <v>101700</v>
+      </c>
+      <c r="E89" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F89" t="n" s="7">
+        <v>10202016</v>
+      </c>
+      <c r="G89" t="str" s="3">
+        <v>春脉绵生：冷却时间降低15%。</v>
+      </c>
+      <c r="H89" t="n" s="7">
+        <v>82010085</v>
+      </c>
+      <c r="I89" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J89" t="n" s="7">
+        <v>10703184</v>
+      </c>
+      <c r="K89" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="7"/>
+      <c r="B90" t="n" s="7">
+        <v>92010086</v>
+      </c>
+      <c r="C90" t="str" s="7">
+        <v>定魄术·双发真意</v>
+      </c>
+      <c r="D90" t="n" s="7">
+        <v>101800</v>
+      </c>
+      <c r="E90" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F90" t="n" s="7">
+        <v>10202017</v>
+      </c>
+      <c r="G90" t="str" s="3">
+        <v>定魄术：连续施放两道定魄术，保留单体锁定规则。</v>
+      </c>
+      <c r="H90" t="n" s="7">
+        <v>82010086</v>
+      </c>
+      <c r="I90" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J90" t="n" s="7">
+        <v>10703185</v>
+      </c>
+      <c r="K90" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="7"/>
+      <c r="B91" t="n" s="7">
+        <v>92010087</v>
+      </c>
+      <c r="C91" t="str" s="7">
+        <v>定魄术·疾射真意</v>
+      </c>
+      <c r="D91" t="n" s="7">
+        <v>101800</v>
+      </c>
+      <c r="E91" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F91" t="n" s="7">
+        <v>10202017</v>
+      </c>
+      <c r="G91" t="str" s="3">
+        <v>定魄术：术法弹道飞行速度提高30%。</v>
+      </c>
+      <c r="H91" t="n" s="7">
+        <v>82010087</v>
+      </c>
+      <c r="I91" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J91" t="n" s="7">
+        <v>10703186</v>
+      </c>
+      <c r="K91" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="7"/>
+      <c r="B92" t="n" s="7">
+        <v>92010088</v>
+      </c>
+      <c r="C92" t="str" s="7">
+        <v>定魄术·远引真意</v>
+      </c>
+      <c r="D92" t="n" s="7">
+        <v>101800</v>
+      </c>
+      <c r="E92" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F92" t="n" s="7">
+        <v>10202017</v>
+      </c>
+      <c r="G92" t="str" s="3">
+        <v>定魄术：施法距离和弹道射程提高20%。</v>
+      </c>
+      <c r="H92" t="n" s="7">
+        <v>82010088</v>
+      </c>
+      <c r="I92" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J92" t="n" s="7">
+        <v>10703187</v>
+      </c>
+      <c r="K92" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="7"/>
+      <c r="B93" t="n" s="7">
+        <v>92010089</v>
+      </c>
+      <c r="C93" t="str" s="7">
+        <v>定魄术·回转真意</v>
+      </c>
+      <c r="D93" t="n" s="7">
+        <v>101800</v>
+      </c>
+      <c r="E93" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F93" t="n" s="7">
+        <v>10202017</v>
+      </c>
+      <c r="G93" t="str" s="3">
+        <v>定魄术：冷却时间降低15%。</v>
+      </c>
+      <c r="H93" t="n" s="7">
+        <v>82010089</v>
+      </c>
+      <c r="I93" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J93" t="n" s="7">
+        <v>10703188</v>
+      </c>
+      <c r="K93" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="7"/>
+      <c r="B94" t="n" s="7">
+        <v>92010090</v>
+      </c>
+      <c r="C94" t="str" s="7">
+        <v>定魄术·广域真意</v>
+      </c>
+      <c r="D94" t="n" s="7">
+        <v>101800</v>
+      </c>
+      <c r="E94" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F94" t="n" s="7">
+        <v>10202017</v>
+      </c>
+      <c r="G94" t="str" s="3">
+        <v>定魄术：术法弹道碰撞命中半径提高25%。</v>
+      </c>
+      <c r="H94" t="n" s="7">
+        <v>82010090</v>
+      </c>
+      <c r="I94" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J94" t="n" s="7">
+        <v>10703189</v>
+      </c>
+      <c r="K94" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="7"/>
+      <c r="B95" t="n" s="7">
+        <v>92010091</v>
+      </c>
+      <c r="C95" t="str" s="7">
+        <v>霜锁九脉·广霜真意</v>
+      </c>
+      <c r="D95" t="n" s="7">
+        <v>101900</v>
+      </c>
+      <c r="E95" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F95" t="n" s="7">
+        <v>10202018</v>
+      </c>
+      <c r="G95" t="str" s="3">
+        <v>霜锁九脉：冰冻圈半径提高25%。</v>
+      </c>
+      <c r="H95" t="n" s="7">
+        <v>82010091</v>
+      </c>
+      <c r="I95" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J95" t="n" s="7">
+        <v>10703190</v>
+      </c>
+      <c r="K95" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="7"/>
+      <c r="B96" t="n" s="7">
+        <v>92010092</v>
+      </c>
+      <c r="C96" t="str" s="7">
+        <v>霜锁九脉·凝霜真意</v>
+      </c>
+      <c r="D96" t="n" s="7">
+        <v>101900</v>
+      </c>
+      <c r="E96" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F96" t="n" s="7">
+        <v>10202018</v>
+      </c>
+      <c r="G96" t="str" s="3">
+        <v>霜锁九脉：冰冻持续时间提高20%。</v>
+      </c>
+      <c r="H96" t="n" s="7">
+        <v>82010092</v>
+      </c>
+      <c r="I96" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J96" t="n" s="7">
+        <v>10703191</v>
+      </c>
+      <c r="K96" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="7"/>
+      <c r="B97" t="n" s="7">
+        <v>92010093</v>
+      </c>
+      <c r="C97" t="str" s="7">
+        <v>霜锁九脉·遥霜真意</v>
+      </c>
+      <c r="D97" t="n" s="7">
+        <v>101900</v>
+      </c>
+      <c r="E97" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F97" t="n" s="7">
+        <v>10202018</v>
+      </c>
+      <c r="G97" t="str" s="3">
+        <v>霜锁九脉：施法距离提高20%。</v>
+      </c>
+      <c r="H97" t="n" s="7">
+        <v>82010093</v>
+      </c>
+      <c r="I97" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J97" t="n" s="7">
+        <v>10703192</v>
+      </c>
+      <c r="K97" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="7"/>
+      <c r="B98" t="n" s="7">
+        <v>92010094</v>
+      </c>
+      <c r="C98" t="str" s="7">
+        <v>霜锁九脉·回霜真意</v>
+      </c>
+      <c r="D98" t="n" s="7">
+        <v>101900</v>
+      </c>
+      <c r="E98" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F98" t="n" s="7">
+        <v>10202018</v>
+      </c>
+      <c r="G98" t="str" s="3">
+        <v>霜锁九脉：冷却时间降低15%。</v>
+      </c>
+      <c r="H98" t="n" s="7">
+        <v>82010094</v>
+      </c>
+      <c r="I98" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J98" t="n" s="7">
+        <v>10703193</v>
+      </c>
+      <c r="K98" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="7"/>
+      <c r="B99" t="n" s="7">
+        <v>92010095</v>
+      </c>
+      <c r="C99" t="str" s="7">
+        <v>霜锁九脉·寒蚀真意</v>
+      </c>
+      <c r="D99" t="n" s="7">
+        <v>101900</v>
+      </c>
+      <c r="E99" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F99" t="n" s="7">
+        <v>10202018</v>
+      </c>
+      <c r="G99" t="str" s="3">
+        <v>霜锁九脉：冰冻同时附加短时法防降低。</v>
+      </c>
+      <c r="H99" t="n" s="7">
+        <v>82010095</v>
+      </c>
+      <c r="I99" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J99" t="n" s="7">
+        <v>10703194</v>
+      </c>
+      <c r="K99" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="7"/>
+      <c r="B100" t="n" s="7">
+        <v>92010096</v>
+      </c>
+      <c r="C100" t="str" s="7">
+        <v>砺锋诀·久锋真意</v>
+      </c>
+      <c r="D100" t="n" s="7">
+        <v>102000</v>
+      </c>
+      <c r="E100" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F100" t="n" s="7">
+        <v>10202019</v>
+      </c>
+      <c r="G100" t="str" s="3">
+        <v>砺锋诀：攻击强化持续时间提高25%。</v>
+      </c>
+      <c r="H100" t="n" s="7">
+        <v>82010096</v>
+      </c>
+      <c r="I100" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J100" t="n" s="7">
+        <v>10703195</v>
+      </c>
+      <c r="K100" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="7"/>
+      <c r="B101" t="n" s="7">
+        <v>92010097</v>
+      </c>
+      <c r="C101" t="str" s="7">
+        <v>砺锋诀·锐锋真意</v>
+      </c>
+      <c r="D101" t="n" s="7">
+        <v>102000</v>
+      </c>
+      <c r="E101" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F101" t="n" s="7">
+        <v>10202019</v>
+      </c>
+      <c r="G101" t="str" s="3">
+        <v>砺锋诀：攻击上下限增幅各额外增加200万分比。</v>
+      </c>
+      <c r="H101" t="n" s="7">
+        <v>82010097</v>
+      </c>
+      <c r="I101" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J101" t="n" s="7">
+        <v>10703196</v>
+      </c>
+      <c r="K101" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="7"/>
+      <c r="B102" t="n" s="7">
+        <v>92010098</v>
+      </c>
+      <c r="C102" t="str" s="7">
+        <v>砺锋诀·回锋真意</v>
+      </c>
+      <c r="D102" t="n" s="7">
+        <v>102000</v>
+      </c>
+      <c r="E102" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F102" t="n" s="7">
+        <v>10202019</v>
+      </c>
+      <c r="G102" t="str" s="3">
+        <v>砺锋诀：冷却时间降低15%。</v>
+      </c>
+      <c r="H102" t="n" s="7">
+        <v>82010098</v>
+      </c>
+      <c r="I102" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J102" t="n" s="7">
+        <v>10703197</v>
+      </c>
+      <c r="K102" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="7"/>
+      <c r="B103" t="n" s="7">
+        <v>92010099</v>
+      </c>
+      <c r="C103" t="str" s="7">
+        <v>砺锋诀·聚锋真意</v>
+      </c>
+      <c r="D103" t="n" s="7">
+        <v>102000</v>
+      </c>
+      <c r="E103" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F103" t="n" s="7">
+        <v>10202019</v>
+      </c>
+      <c r="G103" t="str" s="3">
+        <v>砺锋诀：可储存两次使用，单层恢复16000毫秒。</v>
+      </c>
+      <c r="H103" t="n" s="7">
+        <v>82010099</v>
+      </c>
+      <c r="I103" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J103" t="n" s="7">
+        <v>10703198</v>
+      </c>
+      <c r="K103" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="7"/>
+      <c r="B104" t="n" s="7">
+        <v>92010100</v>
+      </c>
+      <c r="C104" t="str" s="7">
+        <v>砺锋诀·护锋真意</v>
+      </c>
+      <c r="D104" t="n" s="7">
+        <v>102000</v>
+      </c>
+      <c r="E104" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F104" t="n" s="7">
+        <v>10202019</v>
+      </c>
+      <c r="G104" t="str" s="3">
+        <v>砺锋诀：原攻击强化仍在，并附加短时小护盾。</v>
+      </c>
+      <c r="H104" t="n" s="7">
+        <v>82010100</v>
+      </c>
+      <c r="I104" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J104" t="n" s="7">
+        <v>10703199</v>
+      </c>
+      <c r="K104" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="7"/>
+      <c r="B105" t="n" s="7">
+        <v>92010101</v>
+      </c>
+      <c r="C105" t="str" s="7">
+        <v>玄炁贯灵·久灵真意</v>
+      </c>
+      <c r="D105" t="n" s="7">
+        <v>102100</v>
+      </c>
+      <c r="E105" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F105" t="n" s="7">
+        <v>10202020</v>
+      </c>
+      <c r="G105" t="str" s="3">
+        <v>玄炁贯灵：法力强化持续时间提高25%。</v>
+      </c>
+      <c r="H105" t="n" s="7">
+        <v>82010101</v>
+      </c>
+      <c r="I105" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J105" t="n" s="7">
+        <v>10703200</v>
+      </c>
+      <c r="K105" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="7"/>
+      <c r="B106" t="n" s="7">
+        <v>92010102</v>
+      </c>
+      <c r="C106" t="str" s="7">
+        <v>玄炁贯灵·贯灵真意</v>
+      </c>
+      <c r="D106" t="n" s="7">
+        <v>102100</v>
+      </c>
+      <c r="E106" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F106" t="n" s="7">
+        <v>10202020</v>
+      </c>
+      <c r="G106" t="str" s="3">
+        <v>玄炁贯灵：法力上下限增幅各额外增加200万分比。</v>
+      </c>
+      <c r="H106" t="n" s="7">
+        <v>82010102</v>
+      </c>
+      <c r="I106" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J106" t="n" s="7">
+        <v>10703201</v>
+      </c>
+      <c r="K106" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="7"/>
+      <c r="B107" t="n" s="7">
+        <v>92010103</v>
+      </c>
+      <c r="C107" t="str" s="7">
+        <v>玄炁贯灵·回灵真意</v>
+      </c>
+      <c r="D107" t="n" s="7">
+        <v>102100</v>
+      </c>
+      <c r="E107" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F107" t="n" s="7">
+        <v>10202020</v>
+      </c>
+      <c r="G107" t="str" s="3">
+        <v>玄炁贯灵：冷却时间降低15%。</v>
+      </c>
+      <c r="H107" t="n" s="7">
+        <v>82010103</v>
+      </c>
+      <c r="I107" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J107" t="n" s="7">
+        <v>10703202</v>
+      </c>
+      <c r="K107" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="7"/>
+      <c r="B108" t="n" s="7">
+        <v>92010104</v>
+      </c>
+      <c r="C108" t="str" s="7">
+        <v>玄炁贯灵·藏灵真意</v>
+      </c>
+      <c r="D108" t="n" s="7">
+        <v>102100</v>
+      </c>
+      <c r="E108" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F108" t="n" s="7">
+        <v>10202020</v>
+      </c>
+      <c r="G108" t="str" s="3">
+        <v>玄炁贯灵：可储存两次使用，单层恢复16000毫秒。</v>
+      </c>
+      <c r="H108" t="n" s="7">
+        <v>82010104</v>
+      </c>
+      <c r="I108" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J108" t="n" s="7">
+        <v>10703203</v>
+      </c>
+      <c r="K108" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="7"/>
+      <c r="B109" t="n" s="7">
+        <v>92010105</v>
+      </c>
+      <c r="C109" t="str" s="7">
+        <v>玄炁贯灵·护灵真意</v>
+      </c>
+      <c r="D109" t="n" s="7">
+        <v>102100</v>
+      </c>
+      <c r="E109" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F109" t="n" s="7">
+        <v>10202020</v>
+      </c>
+      <c r="G109" t="str" s="3">
+        <v>玄炁贯灵：保留法力强化，同时附加短时小护盾。</v>
+      </c>
+      <c r="H109" t="n" s="7">
+        <v>82010105</v>
+      </c>
+      <c r="I109" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J109" t="n" s="7">
+        <v>10703204</v>
+      </c>
+      <c r="K109" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="7"/>
+      <c r="B110" t="n" s="7">
+        <v>92010106</v>
+      </c>
+      <c r="C110" t="str" s="7">
+        <v>破甲印·久裂真意</v>
+      </c>
+      <c r="D110" t="n" s="7">
+        <v>102200</v>
+      </c>
+      <c r="E110" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F110" t="n" s="7">
+        <v>10202021</v>
+      </c>
+      <c r="G110" t="str" s="3">
+        <v>破甲印：物防降低状态持续时间提高25%。</v>
+      </c>
+      <c r="H110" t="n" s="7">
+        <v>82010106</v>
+      </c>
+      <c r="I110" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J110" t="n" s="7">
+        <v>10703205</v>
+      </c>
+      <c r="K110" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="7"/>
+      <c r="B111" t="n" s="7">
+        <v>92010107</v>
+      </c>
+      <c r="C111" t="str" s="7">
+        <v>破甲印·深裂真意</v>
+      </c>
+      <c r="D111" t="n" s="7">
+        <v>102200</v>
+      </c>
+      <c r="E111" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F111" t="n" s="7">
+        <v>10202021</v>
+      </c>
+      <c r="G111" t="str" s="3">
+        <v>破甲印：物防上下限增幅再降低200万分比。</v>
+      </c>
+      <c r="H111" t="n" s="7">
+        <v>82010107</v>
+      </c>
+      <c r="I111" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J111" t="n" s="7">
+        <v>10703206</v>
+      </c>
+      <c r="K111" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="7"/>
+      <c r="B112" t="n" s="7">
+        <v>92010108</v>
+      </c>
+      <c r="C112" t="str" s="7">
+        <v>破甲印·遥裂真意</v>
+      </c>
+      <c r="D112" t="n" s="7">
+        <v>102200</v>
+      </c>
+      <c r="E112" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F112" t="n" s="7">
+        <v>10202021</v>
+      </c>
+      <c r="G112" t="str" s="3">
+        <v>破甲印：施法距离提高20%。</v>
+      </c>
+      <c r="H112" t="n" s="7">
+        <v>82010108</v>
+      </c>
+      <c r="I112" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J112" t="n" s="7">
+        <v>10703207</v>
+      </c>
+      <c r="K112" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="7"/>
+      <c r="B113" t="n" s="7">
+        <v>92010109</v>
+      </c>
+      <c r="C113" t="str" s="7">
+        <v>破甲印·回裂真意</v>
+      </c>
+      <c r="D113" t="n" s="7">
+        <v>102200</v>
+      </c>
+      <c r="E113" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F113" t="n" s="7">
+        <v>10202021</v>
+      </c>
+      <c r="G113" t="str" s="3">
+        <v>破甲印：冷却时间降低15%。</v>
+      </c>
+      <c r="H113" t="n" s="7">
+        <v>82010109</v>
+      </c>
+      <c r="I113" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J113" t="n" s="7">
+        <v>10703208</v>
+      </c>
+      <c r="K113" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="7"/>
+      <c r="B114" t="n" s="7">
+        <v>92010110</v>
+      </c>
+      <c r="C114" t="str" s="7">
+        <v>破甲印·群裂真意</v>
+      </c>
+      <c r="D114" t="n" s="7">
+        <v>102200</v>
+      </c>
+      <c r="E114" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F114" t="n" s="7">
+        <v>10202021</v>
+      </c>
+      <c r="G114" t="str" s="3">
+        <v>破甲印：改为目标点半径180的范围破甲，最多3个敌人。</v>
+      </c>
+      <c r="H114" t="n" s="7">
+        <v>82010110</v>
+      </c>
+      <c r="I114" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J114" t="n" s="7">
+        <v>10703209</v>
+      </c>
+      <c r="K114" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="7"/>
+      <c r="B115" t="n" s="7">
+        <v>92010111</v>
+      </c>
+      <c r="C115" t="str" s="7">
+        <v>蚀法咒·久蚀真意</v>
+      </c>
+      <c r="D115" t="n" s="7">
+        <v>102300</v>
+      </c>
+      <c r="E115" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F115" t="n" s="7">
+        <v>10202022</v>
+      </c>
+      <c r="G115" t="str" s="3">
+        <v>蚀法咒：法防降低状态持续时间提高25%。</v>
+      </c>
+      <c r="H115" t="n" s="7">
+        <v>82010111</v>
+      </c>
+      <c r="I115" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J115" t="n" s="7">
+        <v>10703210</v>
+      </c>
+      <c r="K115" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="7"/>
+      <c r="B116" t="n" s="7">
+        <v>92010112</v>
+      </c>
+      <c r="C116" t="str" s="7">
+        <v>蚀法咒·深蚀真意</v>
+      </c>
+      <c r="D116" t="n" s="7">
+        <v>102300</v>
+      </c>
+      <c r="E116" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F116" t="n" s="7">
+        <v>10202022</v>
+      </c>
+      <c r="G116" t="str" s="3">
+        <v>蚀法咒：法防上下限增幅再降低200万分比。</v>
+      </c>
+      <c r="H116" t="n" s="7">
+        <v>82010112</v>
+      </c>
+      <c r="I116" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J116" t="n" s="7">
+        <v>10703211</v>
+      </c>
+      <c r="K116" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="7"/>
+      <c r="B117" t="n" s="7">
+        <v>92010113</v>
+      </c>
+      <c r="C117" t="str" s="7">
+        <v>蚀法咒·遥蚀真意</v>
+      </c>
+      <c r="D117" t="n" s="7">
+        <v>102300</v>
+      </c>
+      <c r="E117" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F117" t="n" s="7">
+        <v>10202022</v>
+      </c>
+      <c r="G117" t="str" s="3">
+        <v>蚀法咒：施法距离提高20%。</v>
+      </c>
+      <c r="H117" t="n" s="7">
+        <v>82010113</v>
+      </c>
+      <c r="I117" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J117" t="n" s="7">
+        <v>10703212</v>
+      </c>
+      <c r="K117" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="7"/>
+      <c r="B118" t="n" s="7">
+        <v>92010114</v>
+      </c>
+      <c r="C118" t="str" s="7">
+        <v>蚀法咒·回蚀真意</v>
+      </c>
+      <c r="D118" t="n" s="7">
+        <v>102300</v>
+      </c>
+      <c r="E118" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F118" t="n" s="7">
+        <v>10202022</v>
+      </c>
+      <c r="G118" t="str" s="3">
+        <v>蚀法咒：冷却时间降低15%。</v>
+      </c>
+      <c r="H118" t="n" s="7">
+        <v>82010114</v>
+      </c>
+      <c r="I118" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J118" t="n" s="7">
+        <v>10703213</v>
+      </c>
+      <c r="K118" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="7"/>
+      <c r="B119" t="n" s="7">
+        <v>92010115</v>
+      </c>
+      <c r="C119" t="str" s="7">
+        <v>蚀法咒·群蚀真意</v>
+      </c>
+      <c r="D119" t="n" s="7">
+        <v>102300</v>
+      </c>
+      <c r="E119" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F119" t="n" s="7">
+        <v>10202022</v>
+      </c>
+      <c r="G119" t="str" s="3">
+        <v>蚀法咒：改为目标点半径180的范围蚀法，最多3个敌人。</v>
+      </c>
+      <c r="H119" t="n" s="7">
+        <v>82010115</v>
+      </c>
+      <c r="I119" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J119" t="n" s="7">
+        <v>10703214</v>
+      </c>
+      <c r="K119" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="7"/>
+      <c r="B120" t="n" s="7">
+        <v>92010116</v>
+      </c>
+      <c r="C120" t="str" s="7">
+        <v>余烬侵脉·青木真意</v>
+      </c>
+      <c r="D120" t="n" s="7">
+        <v>102400</v>
+      </c>
+      <c r="E120" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F120" t="n" s="7">
+        <v>10202023</v>
+      </c>
+      <c r="G120" t="str" s="3">
+        <v>余烬侵脉：持续伤害的发起神通改属木行，伤害通道保持。</v>
+      </c>
+      <c r="H120" t="n" s="7">
+        <v>82010116</v>
+      </c>
+      <c r="I120" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J120" t="n" s="7">
+        <v>10703215</v>
+      </c>
+      <c r="K120" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="7"/>
+      <c r="B121" t="n" s="7">
+        <v>92010117</v>
+      </c>
+      <c r="C121" t="str" s="7">
+        <v>余烬侵脉·庚金真意</v>
+      </c>
+      <c r="D121" t="n" s="7">
+        <v>102400</v>
+      </c>
+      <c r="E121" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F121" t="n" s="7">
+        <v>10202023</v>
+      </c>
+      <c r="G121" t="str" s="3">
+        <v>余烬侵脉：持续伤害的发起神通改属金行，伤害通道保持。</v>
+      </c>
+      <c r="H121" t="n" s="7">
+        <v>82010117</v>
+      </c>
+      <c r="I121" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J121" t="n" s="7">
+        <v>10703216</v>
+      </c>
+      <c r="K121" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="7"/>
+      <c r="B122" t="n" s="7">
+        <v>92010118</v>
+      </c>
+      <c r="C122" t="str" s="7">
+        <v>余烬侵脉·久烬真意</v>
+      </c>
+      <c r="D122" t="n" s="7">
+        <v>102400</v>
+      </c>
+      <c r="E122" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F122" t="n" s="7">
+        <v>10202023</v>
+      </c>
+      <c r="G122" t="str" s="3">
+        <v>余烬侵脉：持续伤害状态时长提高25%。</v>
+      </c>
+      <c r="H122" t="n" s="7">
+        <v>82010118</v>
+      </c>
+      <c r="I122" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J122" t="n" s="7">
+        <v>10703217</v>
+      </c>
+      <c r="K122" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="7"/>
+      <c r="B123" t="n" s="7">
+        <v>92010119</v>
+      </c>
+      <c r="C123" t="str" s="7">
+        <v>余烬侵脉·炽烬真意</v>
+      </c>
+      <c r="D123" t="n" s="7">
+        <v>102400</v>
+      </c>
+      <c r="E123" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F123" t="n" s="7">
+        <v>10202023</v>
+      </c>
+      <c r="G123" t="str" s="3">
+        <v>余烬侵脉：持续伤害系数提高15%。</v>
+      </c>
+      <c r="H123" t="n" s="7">
+        <v>82010119</v>
+      </c>
+      <c r="I123" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J123" t="n" s="7">
+        <v>10703218</v>
+      </c>
+      <c r="K123" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="7"/>
+      <c r="B124" t="n" s="7">
+        <v>92010120</v>
+      </c>
+      <c r="C124" t="str" s="7">
+        <v>余烬侵脉·急烬真意</v>
+      </c>
+      <c r="D124" t="n" s="7">
+        <v>102400</v>
+      </c>
+      <c r="E124" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F124" t="n" s="7">
+        <v>10202023</v>
+      </c>
+      <c r="G124" t="str" s="3">
+        <v>余烬侵脉：持续伤害间隔降低20%。</v>
+      </c>
+      <c r="H124" t="n" s="7">
+        <v>82010120</v>
+      </c>
+      <c r="I124" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J124" t="n" s="7">
+        <v>10703219</v>
+      </c>
+      <c r="K124" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="7"/>
+      <c r="B125" t="n" s="7">
+        <v>92010121</v>
+      </c>
+      <c r="C125" t="str" s="7">
+        <v>离焰周身·庚金真意</v>
+      </c>
+      <c r="D125" t="n" s="7">
+        <v>102500</v>
+      </c>
+      <c r="E125" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F125" t="n" s="7">
+        <v>10202024</v>
+      </c>
+      <c r="G125" t="str" s="3">
+        <v>离焰周身：周身焰轮改属金行。</v>
+      </c>
+      <c r="H125" t="n" s="7">
+        <v>82010121</v>
+      </c>
+      <c r="I125" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J125" t="n" s="7">
+        <v>10703220</v>
+      </c>
+      <c r="K125" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="7"/>
+      <c r="B126" t="n" s="7">
+        <v>92010122</v>
+      </c>
+      <c r="C126" t="str" s="7">
+        <v>离焰周身·玄水真意</v>
+      </c>
+      <c r="D126" t="n" s="7">
+        <v>102500</v>
+      </c>
+      <c r="E126" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F126" t="n" s="7">
+        <v>10202024</v>
+      </c>
+      <c r="G126" t="str" s="3">
+        <v>离焰周身：周身焰轮改属水行。</v>
+      </c>
+      <c r="H126" t="n" s="7">
+        <v>82010122</v>
+      </c>
+      <c r="I126" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J126" t="n" s="7">
+        <v>10703221</v>
+      </c>
+      <c r="K126" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="7"/>
+      <c r="B127" t="n" s="7">
+        <v>92010123</v>
+      </c>
+      <c r="C127" t="str" s="7">
+        <v>离焰周身·久焰真意</v>
+      </c>
+      <c r="D127" t="n" s="7">
+        <v>102500</v>
+      </c>
+      <c r="E127" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F127" t="n" s="7">
+        <v>10202024</v>
+      </c>
+      <c r="G127" t="str" s="3">
+        <v>离焰周身：焰轮状态持续时间提高25%。</v>
+      </c>
+      <c r="H127" t="n" s="7">
+        <v>82010123</v>
+      </c>
+      <c r="I127" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J127" t="n" s="7">
+        <v>10703222</v>
+      </c>
+      <c r="K127" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="7"/>
+      <c r="B128" t="n" s="7">
+        <v>92010124</v>
+      </c>
+      <c r="C128" t="str" s="7">
+        <v>离焰周身·急焰真意</v>
+      </c>
+      <c r="D128" t="n" s="7">
+        <v>102500</v>
+      </c>
+      <c r="E128" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F128" t="n" s="7">
+        <v>10202024</v>
+      </c>
+      <c r="G128" t="str" s="3">
+        <v>离焰周身：焰轮触发间隔降低20%。</v>
+      </c>
+      <c r="H128" t="n" s="7">
+        <v>82010124</v>
+      </c>
+      <c r="I128" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J128" t="n" s="7">
+        <v>10703223</v>
+      </c>
+      <c r="K128" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="7"/>
+      <c r="B129" t="n" s="7">
+        <v>92010125</v>
+      </c>
+      <c r="C129" t="str" s="7">
+        <v>离焰周身·回焰真意</v>
+      </c>
+      <c r="D129" t="n" s="7">
+        <v>102500</v>
+      </c>
+      <c r="E129" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F129" t="n" s="7">
+        <v>10202024</v>
+      </c>
+      <c r="G129" t="str" s="3">
+        <v>离焰周身：冷却时间降低15%。</v>
+      </c>
+      <c r="H129" t="n" s="7">
+        <v>82010125</v>
+      </c>
+      <c r="I129" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J129" t="n" s="7">
+        <v>10703224</v>
+      </c>
+      <c r="K129" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="7"/>
+      <c r="B130" t="n" s="7">
+        <v>92010126</v>
+      </c>
+      <c r="C130" t="str" s="7">
+        <v>玄霜蚀法·久环真意</v>
+      </c>
+      <c r="D130" t="n" s="7">
+        <v>102600</v>
+      </c>
+      <c r="E130" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F130" t="n" s="7">
+        <v>10202025</v>
+      </c>
+      <c r="G130" t="str" s="3">
+        <v>玄霜蚀法：霜环持续时间提高25%。</v>
+      </c>
+      <c r="H130" t="n" s="7">
+        <v>82010126</v>
+      </c>
+      <c r="I130" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J130" t="n" s="7">
+        <v>10703225</v>
+      </c>
+      <c r="K130" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="7"/>
+      <c r="B131" t="n" s="7">
+        <v>92010127</v>
+      </c>
+      <c r="C131" t="str" s="7">
+        <v>玄霜蚀法·急环真意</v>
+      </c>
+      <c r="D131" t="n" s="7">
+        <v>102600</v>
+      </c>
+      <c r="E131" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F131" t="n" s="7">
+        <v>10202025</v>
+      </c>
+      <c r="G131" t="str" s="3">
+        <v>玄霜蚀法：霜环触发间隔降低20%。</v>
+      </c>
+      <c r="H131" t="n" s="7">
+        <v>82010127</v>
+      </c>
+      <c r="I131" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J131" t="n" s="7">
+        <v>10703226</v>
+      </c>
+      <c r="K131" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="7"/>
+      <c r="B132" t="n" s="7">
+        <v>92010128</v>
+      </c>
+      <c r="C132" t="str" s="7">
+        <v>玄霜蚀法·回环真意</v>
+      </c>
+      <c r="D132" t="n" s="7">
+        <v>102600</v>
+      </c>
+      <c r="E132" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F132" t="n" s="7">
+        <v>10202025</v>
+      </c>
+      <c r="G132" t="str" s="3">
+        <v>玄霜蚀法：冷却时间降低15%。</v>
+      </c>
+      <c r="H132" t="n" s="7">
+        <v>82010128</v>
+      </c>
+      <c r="I132" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J132" t="n" s="7">
+        <v>10703227</v>
+      </c>
+      <c r="K132" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="7"/>
+      <c r="B133" t="n" s="7">
+        <v>92010129</v>
+      </c>
+      <c r="C133" t="str" s="7">
+        <v>玄霜蚀法·蓄环真意</v>
+      </c>
+      <c r="D133" t="n" s="7">
+        <v>102600</v>
+      </c>
+      <c r="E133" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F133" t="n" s="7">
+        <v>10202025</v>
+      </c>
+      <c r="G133" t="str" s="3">
+        <v>玄霜蚀法：可储存两次释放，单层恢复16000毫秒。</v>
+      </c>
+      <c r="H133" t="n" s="7">
+        <v>82010129</v>
+      </c>
+      <c r="I133" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J133" t="n" s="7">
+        <v>10703228</v>
+      </c>
+      <c r="K133" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="7"/>
+      <c r="B134" t="n" s="7">
+        <v>92010130</v>
+      </c>
+      <c r="C134" t="str" s="7">
+        <v>玄霜蚀法·凝护真意</v>
+      </c>
+      <c r="D134" t="n" s="7">
+        <v>102600</v>
+      </c>
+      <c r="E134" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F134" t="n" s="7">
+        <v>10202025</v>
+      </c>
+      <c r="G134" t="str" s="3">
+        <v>玄霜蚀法：霜环起手同时给自身一层短时小护盾。</v>
+      </c>
+      <c r="H134" t="n" s="7">
+        <v>82010130</v>
+      </c>
+      <c r="I134" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J134" t="n" s="7">
+        <v>10703229</v>
+      </c>
+      <c r="K134" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="7"/>
+      <c r="B135" t="n" s="7">
+        <v>92010131</v>
+      </c>
+      <c r="C135" t="str" s="7">
+        <v>坤岳辟界阵·久阵真意</v>
+      </c>
+      <c r="D135" t="n" s="7">
+        <v>102700</v>
+      </c>
+      <c r="E135" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F135" t="n" s="7">
+        <v>10202026</v>
+      </c>
+      <c r="G135" t="str" s="3">
+        <v>坤岳辟界阵：推敌阵纹持续时间提高25%。</v>
+      </c>
+      <c r="H135" t="n" s="7">
+        <v>82010131</v>
+      </c>
+      <c r="I135" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J135" t="n" s="7">
+        <v>10703230</v>
+      </c>
+      <c r="K135" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="7"/>
+      <c r="B136" t="n" s="7">
+        <v>92010132</v>
+      </c>
+      <c r="C136" t="str" s="7">
+        <v>坤岳辟界阵·急阵真意</v>
+      </c>
+      <c r="D136" t="n" s="7">
+        <v>102700</v>
+      </c>
+      <c r="E136" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F136" t="n" s="7">
+        <v>10202026</v>
+      </c>
+      <c r="G136" t="str" s="3">
+        <v>坤岳辟界阵：阵纹推敌触发间隔降低20%。</v>
+      </c>
+      <c r="H136" t="n" s="7">
+        <v>82010132</v>
+      </c>
+      <c r="I136" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J136" t="n" s="7">
+        <v>10703231</v>
+      </c>
+      <c r="K136" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="7"/>
+      <c r="B137" t="n" s="7">
+        <v>92010133</v>
+      </c>
+      <c r="C137" t="str" s="7">
+        <v>坤岳辟界阵·回阵真意</v>
+      </c>
+      <c r="D137" t="n" s="7">
+        <v>102700</v>
+      </c>
+      <c r="E137" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F137" t="n" s="7">
+        <v>10202026</v>
+      </c>
+      <c r="G137" t="str" s="3">
+        <v>坤岳辟界阵：冷却时间降低15%。</v>
+      </c>
+      <c r="H137" t="n" s="7">
+        <v>82010133</v>
+      </c>
+      <c r="I137" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J137" t="n" s="7">
+        <v>10703232</v>
+      </c>
+      <c r="K137" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="7"/>
+      <c r="B138" t="n" s="7">
+        <v>92010134</v>
+      </c>
+      <c r="C138" t="str" s="7">
+        <v>坤岳辟界阵·蓄阵真意</v>
+      </c>
+      <c r="D138" t="n" s="7">
+        <v>102700</v>
+      </c>
+      <c r="E138" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F138" t="n" s="7">
+        <v>10202026</v>
+      </c>
+      <c r="G138" t="str" s="3">
+        <v>坤岳辟界阵：可储存两次释放，单层恢复16000毫秒。</v>
+      </c>
+      <c r="H138" t="n" s="7">
+        <v>82010134</v>
+      </c>
+      <c r="I138" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J138" t="n" s="7">
+        <v>10703233</v>
+      </c>
+      <c r="K138" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="7"/>
+      <c r="B139" t="n" s="7">
+        <v>92010135</v>
+      </c>
+      <c r="C139" t="str" s="7">
+        <v>坤岳辟界阵·壁阵真意</v>
+      </c>
+      <c r="D139" t="n" s="7">
+        <v>102700</v>
+      </c>
+      <c r="E139" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F139" t="n" s="7">
+        <v>10202026</v>
+      </c>
+      <c r="G139" t="str" s="3">
+        <v>坤岳辟界阵：阵纹起手同时给自身一层短时小护盾。</v>
+      </c>
+      <c r="H139" t="n" s="7">
+        <v>82010135</v>
+      </c>
+      <c r="I139" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J139" t="n" s="7">
+        <v>10703234</v>
+      </c>
+      <c r="K139" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="7"/>
+      <c r="B140" t="n" s="7">
+        <v>92010136</v>
+      </c>
+      <c r="C140" t="str" s="7">
+        <v>游身九转·远游真意</v>
+      </c>
+      <c r="D140" t="n" s="7">
+        <v>102800</v>
+      </c>
+      <c r="E140" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F140" t="n" s="7">
+        <v>10202027</v>
+      </c>
+      <c r="G140" t="str" s="3">
+        <v>游身九转：位移距离提高25%。</v>
+      </c>
+      <c r="H140" t="n" s="7">
+        <v>82010136</v>
+      </c>
+      <c r="I140" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J140" t="n" s="7">
+        <v>10703235</v>
+      </c>
+      <c r="K140" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="7"/>
+      <c r="B141" t="n" s="7">
+        <v>92010137</v>
+      </c>
+      <c r="C141" t="str" s="7">
+        <v>游身九转·疾游真意</v>
+      </c>
+      <c r="D141" t="n" s="7">
+        <v>102800</v>
+      </c>
+      <c r="E141" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F141" t="n" s="7">
+        <v>10202027</v>
+      </c>
+      <c r="G141" t="str" s="3">
+        <v>游身九转：位移速度提高30%，距离不变。</v>
+      </c>
+      <c r="H141" t="n" s="7">
+        <v>82010137</v>
+      </c>
+      <c r="I141" t="n" s="7">
+        <v>1</v>
+      </c>
+      <c r="J141" t="n" s="7">
+        <v>10703236</v>
+      </c>
+      <c r="K141" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="7"/>
+      <c r="B142" t="n" s="7">
+        <v>92010138</v>
+      </c>
+      <c r="C142" t="str" s="7">
+        <v>游身九转·回游真意</v>
+      </c>
+      <c r="D142" t="n" s="7">
+        <v>102800</v>
+      </c>
+      <c r="E142" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F142" t="n" s="7">
+        <v>10202027</v>
+      </c>
+      <c r="G142" t="str" s="3">
+        <v>游身九转：冷却时间降低15%。</v>
+      </c>
+      <c r="H142" t="n" s="7">
+        <v>82010138</v>
+      </c>
+      <c r="I142" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J142" t="n" s="7">
+        <v>10703237</v>
+      </c>
+      <c r="K142" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="7"/>
+      <c r="B143" t="n" s="7">
+        <v>92010139</v>
+      </c>
+      <c r="C143" t="str" s="7">
+        <v>游身九转·双游真意</v>
+      </c>
+      <c r="D143" t="n" s="7">
+        <v>102800</v>
+      </c>
+      <c r="E143" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F143" t="n" s="7">
+        <v>10202027</v>
+      </c>
+      <c r="G143" t="str" s="3">
+        <v>游身九转：可储存两次位移，单层恢复7000毫秒。</v>
+      </c>
+      <c r="H143" t="n" s="7">
+        <v>82010139</v>
+      </c>
+      <c r="I143" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J143" t="n" s="7">
+        <v>10703238</v>
+      </c>
+      <c r="K143" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="7"/>
+      <c r="B144" t="n" s="7">
+        <v>92010140</v>
+      </c>
+      <c r="C144" t="str" s="7">
+        <v>游身九转·护游真意</v>
+      </c>
+      <c r="D144" t="n" s="7">
+        <v>102800</v>
+      </c>
+      <c r="E144" t="str" s="7">
+        <v>玄品</v>
+      </c>
+      <c r="F144" t="n" s="7">
+        <v>10202027</v>
+      </c>
+      <c r="G144" t="str" s="3">
+        <v>游身九转：位移起手给自身一层短时小护盾。</v>
+      </c>
+      <c r="H144" t="n" s="7">
+        <v>82010140</v>
+      </c>
+      <c r="I144" t="n" s="7">
+        <v>2</v>
+      </c>
+      <c r="J144" t="n" s="7">
+        <v>10703239</v>
+      </c>
+      <c r="K144" t="str" s="3">
+        <v>设计提案；全部等级共用，真意只作用玩家主动施放</v>
       </c>
     </row>
   </sheetData>
@@ -1785,4 +6395,2417 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="40" customHeight="1">
+      <x:c r="A1" s="17" t="str">
+        <x:v>真意ID</x:v>
+      </x:c>
+      <x:c r="B1" s="17" t="str">
+        <x:v>词条ID</x:v>
+      </x:c>
+      <x:c r="C1" s="17" t="str">
+        <x:v>激活物品ID</x:v>
+      </x:c>
+      <x:c r="D1" s="17" t="str">
+        <x:v>物品名</x:v>
+      </x:c>
+      <x:c r="E1" s="17" t="str">
+        <x:v>神通识别ID</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="38" customHeight="1">
+      <x:c r="A2" s="15" t="n">
+        <x:v>92010001</x:v>
+      </x:c>
+      <x:c r="B2" s="15" t="n">
+        <x:v>82010001</x:v>
+      </x:c>
+      <x:c r="C2" s="15" t="n">
+        <x:v>10703100</x:v>
+      </x:c>
+      <x:c r="D2" s="15" t="str">
+        <x:v>青萍剑诀·庚金真意残卷</x:v>
+      </x:c>
+      <x:c r="E2" s="15" t="n">
+        <x:v>100100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="38" customHeight="1">
+      <x:c r="A3" s="15" t="n">
+        <x:v>92010002</x:v>
+      </x:c>
+      <x:c r="B3" s="15" t="n">
+        <x:v>82010002</x:v>
+      </x:c>
+      <x:c r="C3" s="15" t="n">
+        <x:v>10703101</x:v>
+      </x:c>
+      <x:c r="D3" s="15" t="str">
+        <x:v>青萍剑诀·离火真意残卷</x:v>
+      </x:c>
+      <x:c r="E3" s="15" t="n">
+        <x:v>100100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="38" customHeight="1">
+      <x:c r="A4" s="15" t="n">
+        <x:v>92010003</x:v>
+      </x:c>
+      <x:c r="B4" s="15" t="n">
+        <x:v>82010003</x:v>
+      </x:c>
+      <x:c r="C4" s="15" t="n">
+        <x:v>10703102</x:v>
+      </x:c>
+      <x:c r="D4" s="15" t="str">
+        <x:v>青萍剑诀·长锋真意残卷</x:v>
+      </x:c>
+      <x:c r="E4" s="15" t="n">
+        <x:v>100100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="38" customHeight="1">
+      <x:c r="A5" s="15" t="n">
+        <x:v>92010004</x:v>
+      </x:c>
+      <x:c r="B5" s="15" t="n">
+        <x:v>82010004</x:v>
+      </x:c>
+      <x:c r="C5" s="15" t="n">
+        <x:v>10703103</x:v>
+      </x:c>
+      <x:c r="D5" s="15" t="str">
+        <x:v>青萍剑诀·聚锋真意残卷</x:v>
+      </x:c>
+      <x:c r="E5" s="15" t="n">
+        <x:v>100100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="38" customHeight="1">
+      <x:c r="A6" s="15" t="n">
+        <x:v>92010005</x:v>
+      </x:c>
+      <x:c r="B6" s="15" t="n">
+        <x:v>82010005</x:v>
+      </x:c>
+      <x:c r="C6" s="15" t="n">
+        <x:v>10703104</x:v>
+      </x:c>
+      <x:c r="D6" s="15" t="str">
+        <x:v>青萍剑诀·影锋真意残卷</x:v>
+      </x:c>
+      <x:c r="E6" s="15" t="n">
+        <x:v>100100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="38" customHeight="1">
+      <x:c r="A7" s="15" t="n">
+        <x:v>92010006</x:v>
+      </x:c>
+      <x:c r="B7" s="15" t="n">
+        <x:v>82010006</x:v>
+      </x:c>
+      <x:c r="C7" s="15" t="n">
+        <x:v>10703105</x:v>
+      </x:c>
+      <x:c r="D7" s="15" t="str">
+        <x:v>玄门伏虎击·庚金真意残卷</x:v>
+      </x:c>
+      <x:c r="E7" s="15" t="n">
+        <x:v>100200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="38" customHeight="1">
+      <x:c r="A8" s="15" t="n">
+        <x:v>92010007</x:v>
+      </x:c>
+      <x:c r="B8" s="15" t="n">
+        <x:v>82010007</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="n">
+        <x:v>10703106</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="str">
+        <x:v>玄门伏虎击·离火真意残卷</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="n">
+        <x:v>100200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="38" customHeight="1">
+      <x:c r="A9" s="15" t="n">
+        <x:v>92010008</x:v>
+      </x:c>
+      <x:c r="B9" s="15" t="n">
+        <x:v>82010008</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="n">
+        <x:v>10703107</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="str">
+        <x:v>玄门伏虎击·震圈真意残卷</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="n">
+        <x:v>100200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="38" customHeight="1">
+      <x:c r="A10" s="15" t="n">
+        <x:v>92010009</x:v>
+      </x:c>
+      <x:c r="B10" s="15" t="n">
+        <x:v>82010009</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="n">
+        <x:v>10703108</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="str">
+        <x:v>玄门伏虎击·重拳真意残卷</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="n">
+        <x:v>100200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="38" customHeight="1">
+      <x:c r="A11" s="15" t="n">
+        <x:v>92010010</x:v>
+      </x:c>
+      <x:c r="B11" s="15" t="n">
+        <x:v>82010010</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="n">
+        <x:v>10703109</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="str">
+        <x:v>玄门伏虎击·余震真意残卷</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="n">
+        <x:v>100200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="38" customHeight="1">
+      <x:c r="A12" s="15" t="n">
+        <x:v>92010011</x:v>
+      </x:c>
+      <x:c r="B12" s="15" t="n">
+        <x:v>82010011</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="n">
+        <x:v>10703110</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="str">
+        <x:v>太白藏锋斩·庚金真意残卷</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="n">
+        <x:v>100300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="38" customHeight="1">
+      <x:c r="A13" s="15" t="n">
+        <x:v>92010012</x:v>
+      </x:c>
+      <x:c r="B13" s="15" t="n">
+        <x:v>82010012</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="n">
+        <x:v>10703111</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="str">
+        <x:v>太白藏锋斩·离火真意残卷</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="n">
+        <x:v>100300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="38" customHeight="1">
+      <x:c r="A14" s="15" t="n">
+        <x:v>92010013</x:v>
+      </x:c>
+      <x:c r="B14" s="15" t="n">
+        <x:v>82010013</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="n">
+        <x:v>10703112</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="str">
+        <x:v>太白藏锋斩·远芒真意残卷</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="n">
+        <x:v>100300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="38" customHeight="1">
+      <x:c r="A15" s="15" t="n">
+        <x:v>92010014</x:v>
+      </x:c>
+      <x:c r="B15" s="15" t="n">
+        <x:v>82010014</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="n">
+        <x:v>10703113</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="str">
+        <x:v>太白藏锋斩·贯锋真意残卷</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="n">
+        <x:v>100300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="38" customHeight="1">
+      <x:c r="A16" s="15" t="n">
+        <x:v>92010015</x:v>
+      </x:c>
+      <x:c r="B16" s="15" t="n">
+        <x:v>82010015</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="n">
+        <x:v>10703114</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="str">
+        <x:v>太白藏锋斩·疾芒真意残卷</x:v>
+      </x:c>
+      <x:c r="E16" s="15" t="n">
+        <x:v>100300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="38" customHeight="1">
+      <x:c r="A17" s="15" t="n">
+        <x:v>92010016</x:v>
+      </x:c>
+      <x:c r="B17" s="15" t="n">
+        <x:v>82010016</x:v>
+      </x:c>
+      <x:c r="C17" s="15" t="n">
+        <x:v>10703115</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="str">
+        <x:v>玄罡撼岳劲·庚金真意残卷</x:v>
+      </x:c>
+      <x:c r="E17" s="15" t="n">
+        <x:v>100400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="38" customHeight="1">
+      <x:c r="A18" s="15" t="n">
+        <x:v>92010017</x:v>
+      </x:c>
+      <x:c r="B18" s="15" t="n">
+        <x:v>82010017</x:v>
+      </x:c>
+      <x:c r="C18" s="15" t="n">
+        <x:v>10703116</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="str">
+        <x:v>玄罡撼岳劲·离火真意残卷</x:v>
+      </x:c>
+      <x:c r="E18" s="15" t="n">
+        <x:v>100400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="38" customHeight="1">
+      <x:c r="A19" s="15" t="n">
+        <x:v>92010018</x:v>
+      </x:c>
+      <x:c r="B19" s="15" t="n">
+        <x:v>82010018</x:v>
+      </x:c>
+      <x:c r="C19" s="15" t="n">
+        <x:v>10703117</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="str">
+        <x:v>玄罡撼岳劲·长劲真意残卷</x:v>
+      </x:c>
+      <x:c r="E19" s="15" t="n">
+        <x:v>100400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="38" customHeight="1">
+      <x:c r="A20" s="15" t="n">
+        <x:v>92010019</x:v>
+      </x:c>
+      <x:c r="B20" s="15" t="n">
+        <x:v>82010019</x:v>
+      </x:c>
+      <x:c r="C20" s="15" t="n">
+        <x:v>10703118</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="str">
+        <x:v>玄罡撼岳劲·宽劲真意残卷</x:v>
+      </x:c>
+      <x:c r="E20" s="15" t="n">
+        <x:v>100400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="38" customHeight="1">
+      <x:c r="A21" s="15" t="n">
+        <x:v>92010020</x:v>
+      </x:c>
+      <x:c r="B21" s="15" t="n">
+        <x:v>82010020</x:v>
+      </x:c>
+      <x:c r="C21" s="15" t="n">
+        <x:v>10703119</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="str">
+        <x:v>玄罡撼岳劲·震退真意残卷</x:v>
+      </x:c>
+      <x:c r="E21" s="15" t="n">
+        <x:v>100400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="28" customHeight="1">
+      <x:c r="A22" s="15" t="n">
+        <x:v>92010021</x:v>
+      </x:c>
+      <x:c r="B22" s="15" t="n">
+        <x:v>82010021</x:v>
+      </x:c>
+      <x:c r="C22" s="15" t="n">
+        <x:v>10703120</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="str">
+        <x:v>庚芒诀·离火真意残卷</x:v>
+      </x:c>
+      <x:c r="E22" s="15" t="n">
+        <x:v>100500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="28" customHeight="1">
+      <x:c r="A23" s="15" t="n">
+        <x:v>92010022</x:v>
+      </x:c>
+      <x:c r="B23" s="15" t="n">
+        <x:v>82010022</x:v>
+      </x:c>
+      <x:c r="C23" s="15" t="n">
+        <x:v>10703121</x:v>
+      </x:c>
+      <x:c r="D23" s="15" t="str">
+        <x:v>庚芒诀·玄水真意残卷</x:v>
+      </x:c>
+      <x:c r="E23" s="15" t="n">
+        <x:v>100500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="28" customHeight="1">
+      <x:c r="A24" s="15" t="n">
+        <x:v>92010023</x:v>
+      </x:c>
+      <x:c r="B24" s="15" t="n">
+        <x:v>82010023</x:v>
+      </x:c>
+      <x:c r="C24" s="15" t="n">
+        <x:v>10703122</x:v>
+      </x:c>
+      <x:c r="D24" s="15" t="str">
+        <x:v>庚芒诀·长虹真意残卷</x:v>
+      </x:c>
+      <x:c r="E24" s="15" t="n">
+        <x:v>100500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="28" customHeight="1">
+      <x:c r="A25" s="15" t="n">
+        <x:v>92010024</x:v>
+      </x:c>
+      <x:c r="B25" s="15" t="n">
+        <x:v>82010024</x:v>
+      </x:c>
+      <x:c r="C25" s="15" t="n">
+        <x:v>10703123</x:v>
+      </x:c>
+      <x:c r="D25" s="15" t="str">
+        <x:v>庚芒诀·横芒真意残卷</x:v>
+      </x:c>
+      <x:c r="E25" s="15" t="n">
+        <x:v>100500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="28" customHeight="1">
+      <x:c r="A26" s="15" t="n">
+        <x:v>92010025</x:v>
+      </x:c>
+      <x:c r="B26" s="15" t="n">
+        <x:v>82010025</x:v>
+      </x:c>
+      <x:c r="C26" s="15" t="n">
+        <x:v>10703124</x:v>
+      </x:c>
+      <x:c r="D26" s="15" t="str">
+        <x:v>庚芒诀·锐贯真意残卷</x:v>
+      </x:c>
+      <x:c r="E26" s="15" t="n">
+        <x:v>100500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="28" customHeight="1">
+      <x:c r="A27" s="15" t="n">
+        <x:v>92010026</x:v>
+      </x:c>
+      <x:c r="B27" s="15" t="n">
+        <x:v>82010026</x:v>
+      </x:c>
+      <x:c r="C27" s="15" t="n">
+        <x:v>10703125</x:v>
+      </x:c>
+      <x:c r="D27" s="15" t="str">
+        <x:v>青萝引·离火真意残卷</x:v>
+      </x:c>
+      <x:c r="E27" s="15" t="n">
+        <x:v>100600</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="28" customHeight="1">
+      <x:c r="A28" s="15" t="n">
+        <x:v>92010027</x:v>
+      </x:c>
+      <x:c r="B28" s="15" t="n">
+        <x:v>82010027</x:v>
+      </x:c>
+      <x:c r="C28" s="15" t="n">
+        <x:v>10703126</x:v>
+      </x:c>
+      <x:c r="D28" s="15" t="str">
+        <x:v>青萝引·玄水真意残卷</x:v>
+      </x:c>
+      <x:c r="E28" s="15" t="n">
+        <x:v>100600</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="28" customHeight="1">
+      <x:c r="A29" s="15" t="n">
+        <x:v>92010028</x:v>
+      </x:c>
+      <x:c r="B29" s="15" t="n">
+        <x:v>82010028</x:v>
+      </x:c>
+      <x:c r="C29" s="15" t="n">
+        <x:v>10703127</x:v>
+      </x:c>
+      <x:c r="D29" s="15" t="str">
+        <x:v>青萝引·繁萝真意残卷</x:v>
+      </x:c>
+      <x:c r="E29" s="15" t="n">
+        <x:v>100600</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="28" customHeight="1">
+      <x:c r="A30" s="15" t="n">
+        <x:v>92010029</x:v>
+      </x:c>
+      <x:c r="B30" s="15" t="n">
+        <x:v>82010029</x:v>
+      </x:c>
+      <x:c r="C30" s="15" t="n">
+        <x:v>10703128</x:v>
+      </x:c>
+      <x:c r="D30" s="15" t="str">
+        <x:v>青萝引·深刺真意残卷</x:v>
+      </x:c>
+      <x:c r="E30" s="15" t="n">
+        <x:v>100600</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="28" customHeight="1">
+      <x:c r="A31" s="15" t="n">
+        <x:v>92010030</x:v>
+      </x:c>
+      <x:c r="B31" s="15" t="n">
+        <x:v>82010030</x:v>
+      </x:c>
+      <x:c r="C31" s="15" t="n">
+        <x:v>10703129</x:v>
+      </x:c>
+      <x:c r="D31" s="15" t="str">
+        <x:v>青萝引·遥引真意残卷</x:v>
+      </x:c>
+      <x:c r="E31" s="15" t="n">
+        <x:v>100600</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="28" customHeight="1">
+      <x:c r="A32" s="15" t="n">
+        <x:v>92010031</x:v>
+      </x:c>
+      <x:c r="B32" s="15" t="n">
+        <x:v>82010031</x:v>
+      </x:c>
+      <x:c r="C32" s="15" t="n">
+        <x:v>10703130</x:v>
+      </x:c>
+      <x:c r="D32" s="15" t="str">
+        <x:v>听潮印·庚金真意残卷</x:v>
+      </x:c>
+      <x:c r="E32" s="15" t="n">
+        <x:v>100700</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="28" customHeight="1">
+      <x:c r="A33" s="15" t="n">
+        <x:v>92010032</x:v>
+      </x:c>
+      <x:c r="B33" s="15" t="n">
+        <x:v>82010032</x:v>
+      </x:c>
+      <x:c r="C33" s="15" t="n">
+        <x:v>10703131</x:v>
+      </x:c>
+      <x:c r="D33" s="15" t="str">
+        <x:v>听潮印·青木真意残卷</x:v>
+      </x:c>
+      <x:c r="E33" s="15" t="n">
+        <x:v>100700</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="28" customHeight="1">
+      <x:c r="A34" s="15" t="n">
+        <x:v>92010033</x:v>
+      </x:c>
+      <x:c r="B34" s="15" t="n">
+        <x:v>82010033</x:v>
+      </x:c>
+      <x:c r="C34" s="15" t="n">
+        <x:v>10703132</x:v>
+      </x:c>
+      <x:c r="D34" s="15" t="str">
+        <x:v>听潮印·涨潮真意残卷</x:v>
+      </x:c>
+      <x:c r="E34" s="15" t="n">
+        <x:v>100700</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="28" customHeight="1">
+      <x:c r="A35" s="15" t="n">
+        <x:v>92010034</x:v>
+      </x:c>
+      <x:c r="B35" s="15" t="n">
+        <x:v>82010034</x:v>
+      </x:c>
+      <x:c r="C35" s="15" t="n">
+        <x:v>10703133</x:v>
+      </x:c>
+      <x:c r="D35" s="15" t="str">
+        <x:v>听潮印·叠浪真意残卷</x:v>
+      </x:c>
+      <x:c r="E35" s="15" t="n">
+        <x:v>100700</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="28" customHeight="1">
+      <x:c r="A36" s="15" t="n">
+        <x:v>92010035</x:v>
+      </x:c>
+      <x:c r="B36" s="15" t="n">
+        <x:v>82010035</x:v>
+      </x:c>
+      <x:c r="C36" s="15" t="n">
+        <x:v>10703134</x:v>
+      </x:c>
+      <x:c r="D36" s="15" t="str">
+        <x:v>听潮印·潮回真意残卷</x:v>
+      </x:c>
+      <x:c r="E36" s="15" t="n">
+        <x:v>100700</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="28" customHeight="1">
+      <x:c r="A37" s="15" t="n">
+        <x:v>92010036</x:v>
+      </x:c>
+      <x:c r="B37" s="15" t="n">
+        <x:v>82010036</x:v>
+      </x:c>
+      <x:c r="C37" s="15" t="n">
+        <x:v>10703135</x:v>
+      </x:c>
+      <x:c r="D37" s="15" t="str">
+        <x:v>离火星·庚金真意残卷</x:v>
+      </x:c>
+      <x:c r="E37" s="15" t="n">
+        <x:v>100800</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="28" customHeight="1">
+      <x:c r="A38" s="15" t="n">
+        <x:v>92010037</x:v>
+      </x:c>
+      <x:c r="B38" s="15" t="n">
+        <x:v>82010037</x:v>
+      </x:c>
+      <x:c r="C38" s="15" t="n">
+        <x:v>10703136</x:v>
+      </x:c>
+      <x:c r="D38" s="15" t="str">
+        <x:v>离火星·玄水真意残卷</x:v>
+      </x:c>
+      <x:c r="E38" s="15" t="n">
+        <x:v>100800</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="28" customHeight="1">
+      <x:c r="A39" s="15" t="n">
+        <x:v>92010038</x:v>
+      </x:c>
+      <x:c r="B39" s="15" t="n">
+        <x:v>82010038</x:v>
+      </x:c>
+      <x:c r="C39" s="15" t="n">
+        <x:v>10703137</x:v>
+      </x:c>
+      <x:c r="D39" s="15" t="str">
+        <x:v>离火星·双星真意残卷</x:v>
+      </x:c>
+      <x:c r="E39" s="15" t="n">
+        <x:v>100800</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="28" customHeight="1">
+      <x:c r="A40" s="15" t="n">
+        <x:v>92010039</x:v>
+      </x:c>
+      <x:c r="B40" s="15" t="n">
+        <x:v>82010039</x:v>
+      </x:c>
+      <x:c r="C40" s="15" t="n">
+        <x:v>10703138</x:v>
+      </x:c>
+      <x:c r="D40" s="15" t="str">
+        <x:v>离火星·流星真意残卷</x:v>
+      </x:c>
+      <x:c r="E40" s="15" t="n">
+        <x:v>100800</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="28" customHeight="1">
+      <x:c r="A41" s="15" t="n">
+        <x:v>92010040</x:v>
+      </x:c>
+      <x:c r="B41" s="15" t="n">
+        <x:v>82010040</x:v>
+      </x:c>
+      <x:c r="C41" s="15" t="n">
+        <x:v>10703139</x:v>
+      </x:c>
+      <x:c r="D41" s="15" t="str">
+        <x:v>离火星·穿焰真意残卷</x:v>
+      </x:c>
+      <x:c r="E41" s="15" t="n">
+        <x:v>100800</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="28" customHeight="1">
+      <x:c r="A42" s="15" t="n">
+        <x:v>92010041</x:v>
+      </x:c>
+      <x:c r="B42" s="15" t="n">
+        <x:v>82010041</x:v>
+      </x:c>
+      <x:c r="C42" s="15" t="n">
+        <x:v>10703140</x:v>
+      </x:c>
+      <x:c r="D42" s="15" t="str">
+        <x:v>凝岳印·庚金真意残卷</x:v>
+      </x:c>
+      <x:c r="E42" s="15" t="n">
+        <x:v>100900</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="28" customHeight="1">
+      <x:c r="A43" s="15" t="n">
+        <x:v>92010042</x:v>
+      </x:c>
+      <x:c r="B43" s="15" t="n">
+        <x:v>82010042</x:v>
+      </x:c>
+      <x:c r="C43" s="15" t="n">
+        <x:v>10703141</x:v>
+      </x:c>
+      <x:c r="D43" s="15" t="str">
+        <x:v>凝岳印·离火真意残卷</x:v>
+      </x:c>
+      <x:c r="E43" s="15" t="n">
+        <x:v>100900</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="28" customHeight="1">
+      <x:c r="A44" s="15" t="n">
+        <x:v>92010043</x:v>
+      </x:c>
+      <x:c r="B44" s="15" t="n">
+        <x:v>82010043</x:v>
+      </x:c>
+      <x:c r="C44" s="15" t="n">
+        <x:v>10703142</x:v>
+      </x:c>
+      <x:c r="D44" s="15" t="str">
+        <x:v>凝岳印·速坠真意残卷</x:v>
+      </x:c>
+      <x:c r="E44" s="15" t="n">
+        <x:v>100900</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="28" customHeight="1">
+      <x:c r="A45" s="15" t="n">
+        <x:v>92010044</x:v>
+      </x:c>
+      <x:c r="B45" s="15" t="n">
+        <x:v>82010044</x:v>
+      </x:c>
+      <x:c r="C45" s="15" t="n">
+        <x:v>10703143</x:v>
+      </x:c>
+      <x:c r="D45" s="15" t="str">
+        <x:v>凝岳印·遥印真意残卷</x:v>
+      </x:c>
+      <x:c r="E45" s="15" t="n">
+        <x:v>100900</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="28" customHeight="1">
+      <x:c r="A46" s="15" t="n">
+        <x:v>92010045</x:v>
+      </x:c>
+      <x:c r="B46" s="15" t="n">
+        <x:v>82010045</x:v>
+      </x:c>
+      <x:c r="C46" s="15" t="n">
+        <x:v>10703144</x:v>
+      </x:c>
+      <x:c r="D46" s="15" t="str">
+        <x:v>凝岳印·广印真意残卷</x:v>
+      </x:c>
+      <x:c r="E46" s="15" t="n">
+        <x:v>100900</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="38" customHeight="1">
+      <x:c r="A47" s="15" t="n">
+        <x:v>92010046</x:v>
+      </x:c>
+      <x:c r="B47" s="15" t="n">
+        <x:v>82010046</x:v>
+      </x:c>
+      <x:c r="C47" s="15" t="n">
+        <x:v>10703145</x:v>
+      </x:c>
+      <x:c r="D47" s="15" t="str">
+        <x:v>惊蛰落霆·庚金真意残卷</x:v>
+      </x:c>
+      <x:c r="E47" s="15" t="n">
+        <x:v>101000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="38" customHeight="1">
+      <x:c r="A48" s="15" t="n">
+        <x:v>92010047</x:v>
+      </x:c>
+      <x:c r="B48" s="15" t="n">
+        <x:v>82010047</x:v>
+      </x:c>
+      <x:c r="C48" s="15" t="n">
+        <x:v>10703146</x:v>
+      </x:c>
+      <x:c r="D48" s="15" t="str">
+        <x:v>惊蛰落霆·离火真意残卷</x:v>
+      </x:c>
+      <x:c r="E48" s="15" t="n">
+        <x:v>101000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="38" customHeight="1">
+      <x:c r="A49" s="15" t="n">
+        <x:v>92010048</x:v>
+      </x:c>
+      <x:c r="B49" s="15" t="n">
+        <x:v>82010048</x:v>
+      </x:c>
+      <x:c r="C49" s="15" t="n">
+        <x:v>10703147</x:v>
+      </x:c>
+      <x:c r="D49" s="15" t="str">
+        <x:v>惊蛰落霆·雷域真意残卷</x:v>
+      </x:c>
+      <x:c r="E49" s="15" t="n">
+        <x:v>101000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="38" customHeight="1">
+      <x:c r="A50" s="15" t="n">
+        <x:v>92010049</x:v>
+      </x:c>
+      <x:c r="B50" s="15" t="n">
+        <x:v>82010049</x:v>
+      </x:c>
+      <x:c r="C50" s="15" t="n">
+        <x:v>10703148</x:v>
+      </x:c>
+      <x:c r="D50" s="15" t="str">
+        <x:v>惊蛰落霆·雷威真意残卷</x:v>
+      </x:c>
+      <x:c r="E50" s="15" t="n">
+        <x:v>101000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="38" customHeight="1">
+      <x:c r="A51" s="15" t="n">
+        <x:v>92010050</x:v>
+      </x:c>
+      <x:c r="B51" s="15" t="n">
+        <x:v>82010050</x:v>
+      </x:c>
+      <x:c r="C51" s="15" t="n">
+        <x:v>10703149</x:v>
+      </x:c>
+      <x:c r="D51" s="15" t="str">
+        <x:v>惊蛰落霆·惊雷真意残卷</x:v>
+      </x:c>
+      <x:c r="E51" s="15" t="n">
+        <x:v>101000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="38" customHeight="1">
+      <x:c r="A52" s="15" t="n">
+        <x:v>92010051</x:v>
+      </x:c>
+      <x:c r="B52" s="15" t="n">
+        <x:v>82010051</x:v>
+      </x:c>
+      <x:c r="C52" s="15" t="n">
+        <x:v>10703150</x:v>
+      </x:c>
+      <x:c r="D52" s="15" t="str">
+        <x:v>赤霄焚野·青木真意残卷</x:v>
+      </x:c>
+      <x:c r="E52" s="15" t="n">
+        <x:v>101100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="38" customHeight="1">
+      <x:c r="A53" s="15" t="n">
+        <x:v>92010052</x:v>
+      </x:c>
+      <x:c r="B53" s="15" t="n">
+        <x:v>82010052</x:v>
+      </x:c>
+      <x:c r="C53" s="15" t="n">
+        <x:v>10703151</x:v>
+      </x:c>
+      <x:c r="D53" s="15" t="str">
+        <x:v>赤霄焚野·玄水真意残卷</x:v>
+      </x:c>
+      <x:c r="E53" s="15" t="n">
+        <x:v>101100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="38" customHeight="1">
+      <x:c r="A54" s="15" t="n">
+        <x:v>92010053</x:v>
+      </x:c>
+      <x:c r="B54" s="15" t="n">
+        <x:v>82010053</x:v>
+      </x:c>
+      <x:c r="C54" s="15" t="n">
+        <x:v>10703152</x:v>
+      </x:c>
+      <x:c r="D54" s="15" t="str">
+        <x:v>赤霄焚野·急焚真意残卷</x:v>
+      </x:c>
+      <x:c r="E54" s="15" t="n">
+        <x:v>101100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="38" customHeight="1">
+      <x:c r="A55" s="15" t="n">
+        <x:v>92010054</x:v>
+      </x:c>
+      <x:c r="B55" s="15" t="n">
+        <x:v>82010054</x:v>
+      </x:c>
+      <x:c r="C55" s="15" t="n">
+        <x:v>10703153</x:v>
+      </x:c>
+      <x:c r="D55" s="15" t="str">
+        <x:v>赤霄焚野·遥焚真意残卷</x:v>
+      </x:c>
+      <x:c r="E55" s="15" t="n">
+        <x:v>101100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="38" customHeight="1">
+      <x:c r="A56" s="15" t="n">
+        <x:v>92010055</x:v>
+      </x:c>
+      <x:c r="B56" s="15" t="n">
+        <x:v>82010055</x:v>
+      </x:c>
+      <x:c r="C56" s="15" t="n">
+        <x:v>10703154</x:v>
+      </x:c>
+      <x:c r="D56" s="15" t="str">
+        <x:v>赤霄焚野·回焰真意残卷</x:v>
+      </x:c>
+      <x:c r="E56" s="15" t="n">
+        <x:v>101100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="28" customHeight="1">
+      <x:c r="A57" s="15" t="n">
+        <x:v>92010056</x:v>
+      </x:c>
+      <x:c r="B57" s="15" t="n">
+        <x:v>82010056</x:v>
+      </x:c>
+      <x:c r="C57" s="15" t="n">
+        <x:v>10703155</x:v>
+      </x:c>
+      <x:c r="D57" s="15" t="str">
+        <x:v>御锋诀·庚金真意残卷</x:v>
+      </x:c>
+      <x:c r="E57" s="15" t="n">
+        <x:v>101200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="28" customHeight="1">
+      <x:c r="A58" s="15" t="n">
+        <x:v>92010057</x:v>
+      </x:c>
+      <x:c r="B58" s="15" t="n">
+        <x:v>82010057</x:v>
+      </x:c>
+      <x:c r="C58" s="15" t="n">
+        <x:v>10703156</x:v>
+      </x:c>
+      <x:c r="D58" s="15" t="str">
+        <x:v>御锋诀·离火真意残卷</x:v>
+      </x:c>
+      <x:c r="E58" s="15" t="n">
+        <x:v>101200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="28" customHeight="1">
+      <x:c r="A59" s="15" t="n">
+        <x:v>92010058</x:v>
+      </x:c>
+      <x:c r="B59" s="15" t="n">
+        <x:v>82010058</x:v>
+      </x:c>
+      <x:c r="C59" s="15" t="n">
+        <x:v>10703157</x:v>
+      </x:c>
+      <x:c r="D59" s="15" t="str">
+        <x:v>御锋诀·双御真意残卷</x:v>
+      </x:c>
+      <x:c r="E59" s="15" t="n">
+        <x:v>101200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="28" customHeight="1">
+      <x:c r="A60" s="15" t="n">
+        <x:v>92010059</x:v>
+      </x:c>
+      <x:c r="B60" s="15" t="n">
+        <x:v>82010059</x:v>
+      </x:c>
+      <x:c r="C60" s="15" t="n">
+        <x:v>10703158</x:v>
+      </x:c>
+      <x:c r="D60" s="15" t="str">
+        <x:v>御锋诀·疾御真意残卷</x:v>
+      </x:c>
+      <x:c r="E60" s="15" t="n">
+        <x:v>101200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="28" customHeight="1">
+      <x:c r="A61" s="15" t="n">
+        <x:v>92010060</x:v>
+      </x:c>
+      <x:c r="B61" s="15" t="n">
+        <x:v>82010060</x:v>
+      </x:c>
+      <x:c r="C61" s="15" t="n">
+        <x:v>10703159</x:v>
+      </x:c>
+      <x:c r="D61" s="15" t="str">
+        <x:v>御锋诀·远御真意残卷</x:v>
+      </x:c>
+      <x:c r="E61" s="15" t="n">
+        <x:v>101200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="38" customHeight="1">
+      <x:c r="A62" s="15" t="n">
+        <x:v>92010061</x:v>
+      </x:c>
+      <x:c r="B62" s="15" t="n">
+        <x:v>82010061</x:v>
+      </x:c>
+      <x:c r="C62" s="15" t="n">
+        <x:v>10703160</x:v>
+      </x:c>
+      <x:c r="D62" s="15" t="str">
+        <x:v>分光剑诀·庚金真意残卷</x:v>
+      </x:c>
+      <x:c r="E62" s="15" t="n">
+        <x:v>101300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="38" customHeight="1">
+      <x:c r="A63" s="15" t="n">
+        <x:v>92010062</x:v>
+      </x:c>
+      <x:c r="B63" s="15" t="n">
+        <x:v>82010062</x:v>
+      </x:c>
+      <x:c r="C63" s="15" t="n">
+        <x:v>10703161</x:v>
+      </x:c>
+      <x:c r="D63" s="15" t="str">
+        <x:v>分光剑诀·离火真意残卷</x:v>
+      </x:c>
+      <x:c r="E63" s="15" t="n">
+        <x:v>101300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="38" customHeight="1">
+      <x:c r="A64" s="15" t="n">
+        <x:v>92010063</x:v>
+      </x:c>
+      <x:c r="B64" s="15" t="n">
+        <x:v>82010063</x:v>
+      </x:c>
+      <x:c r="C64" s="15" t="n">
+        <x:v>10703162</x:v>
+      </x:c>
+      <x:c r="D64" s="15" t="str">
+        <x:v>分光剑诀·疾影真意残卷</x:v>
+      </x:c>
+      <x:c r="E64" s="15" t="n">
+        <x:v>101300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="38" customHeight="1">
+      <x:c r="A65" s="15" t="n">
+        <x:v>92010064</x:v>
+      </x:c>
+      <x:c r="B65" s="15" t="n">
+        <x:v>82010064</x:v>
+      </x:c>
+      <x:c r="C65" s="15" t="n">
+        <x:v>10703163</x:v>
+      </x:c>
+      <x:c r="D65" s="15" t="str">
+        <x:v>分光剑诀·远影真意残卷</x:v>
+      </x:c>
+      <x:c r="E65" s="15" t="n">
+        <x:v>101300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="38" customHeight="1">
+      <x:c r="A66" s="15" t="n">
+        <x:v>92010065</x:v>
+      </x:c>
+      <x:c r="B66" s="15" t="n">
+        <x:v>82010065</x:v>
+      </x:c>
+      <x:c r="C66" s="15" t="n">
+        <x:v>10703164</x:v>
+      </x:c>
+      <x:c r="D66" s="15" t="str">
+        <x:v>分光剑诀·回光真意残卷</x:v>
+      </x:c>
+      <x:c r="E66" s="15" t="n">
+        <x:v>101300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="38" customHeight="1">
+      <x:c r="A67" s="15" t="n">
+        <x:v>92010066</x:v>
+      </x:c>
+      <x:c r="B67" s="15" t="n">
+        <x:v>82010066</x:v>
+      </x:c>
+      <x:c r="C67" s="15" t="n">
+        <x:v>10703165</x:v>
+      </x:c>
+      <x:c r="D67" s="15" t="str">
+        <x:v>周天游刃·庚金真意残卷</x:v>
+      </x:c>
+      <x:c r="E67" s="15" t="n">
+        <x:v>101400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="38" customHeight="1">
+      <x:c r="A68" s="15" t="n">
+        <x:v>92010067</x:v>
+      </x:c>
+      <x:c r="B68" s="15" t="n">
+        <x:v>82010067</x:v>
+      </x:c>
+      <x:c r="C68" s="15" t="n">
+        <x:v>10703166</x:v>
+      </x:c>
+      <x:c r="D68" s="15" t="str">
+        <x:v>周天游刃·离火真意残卷</x:v>
+      </x:c>
+      <x:c r="E68" s="15" t="n">
+        <x:v>101400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="38" customHeight="1">
+      <x:c r="A69" s="15" t="n">
+        <x:v>92010068</x:v>
+      </x:c>
+      <x:c r="B69" s="15" t="n">
+        <x:v>82010068</x:v>
+      </x:c>
+      <x:c r="C69" s="15" t="n">
+        <x:v>10703167</x:v>
+      </x:c>
+      <x:c r="D69" s="15" t="str">
+        <x:v>周天游刃·添刃真意残卷</x:v>
+      </x:c>
+      <x:c r="E69" s="15" t="n">
+        <x:v>101400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="38" customHeight="1">
+      <x:c r="A70" s="15" t="n">
+        <x:v>92010069</x:v>
+      </x:c>
+      <x:c r="B70" s="15" t="n">
+        <x:v>82010069</x:v>
+      </x:c>
+      <x:c r="C70" s="15" t="n">
+        <x:v>10703168</x:v>
+      </x:c>
+      <x:c r="D70" s="15" t="str">
+        <x:v>周天游刃·急御真意残卷</x:v>
+      </x:c>
+      <x:c r="E70" s="15" t="n">
+        <x:v>101400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="38" customHeight="1">
+      <x:c r="A71" s="15" t="n">
+        <x:v>92010070</x:v>
+      </x:c>
+      <x:c r="B71" s="15" t="n">
+        <x:v>82010070</x:v>
+      </x:c>
+      <x:c r="C71" s="15" t="n">
+        <x:v>10703169</x:v>
+      </x:c>
+      <x:c r="D71" s="15" t="str">
+        <x:v>周天游刃·远游真意残卷</x:v>
+      </x:c>
+      <x:c r="E71" s="15" t="n">
+        <x:v>101400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="38" customHeight="1">
+      <x:c r="A72" s="15" t="n">
+        <x:v>92010071</x:v>
+      </x:c>
+      <x:c r="B72" s="15" t="n">
+        <x:v>82010071</x:v>
+      </x:c>
+      <x:c r="C72" s="15" t="n">
+        <x:v>10703170</x:v>
+      </x:c>
+      <x:c r="D72" s="15" t="str">
+        <x:v>星罗分锋·庚金真意残卷</x:v>
+      </x:c>
+      <x:c r="E72" s="15" t="n">
+        <x:v>101500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="38" customHeight="1">
+      <x:c r="A73" s="15" t="n">
+        <x:v>92010072</x:v>
+      </x:c>
+      <x:c r="B73" s="15" t="n">
+        <x:v>82010072</x:v>
+      </x:c>
+      <x:c r="C73" s="15" t="n">
+        <x:v>10703171</x:v>
+      </x:c>
+      <x:c r="D73" s="15" t="str">
+        <x:v>星罗分锋·离火真意残卷</x:v>
+      </x:c>
+      <x:c r="E73" s="15" t="n">
+        <x:v>101500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="38" customHeight="1">
+      <x:c r="A74" s="15" t="n">
+        <x:v>92010073</x:v>
+      </x:c>
+      <x:c r="B74" s="15" t="n">
+        <x:v>82010073</x:v>
+      </x:c>
+      <x:c r="C74" s="15" t="n">
+        <x:v>10703172</x:v>
+      </x:c>
+      <x:c r="D74" s="15" t="str">
+        <x:v>星罗分锋·密锋真意残卷</x:v>
+      </x:c>
+      <x:c r="E74" s="15" t="n">
+        <x:v>101500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="38" customHeight="1">
+      <x:c r="A75" s="15" t="n">
+        <x:v>92010074</x:v>
+      </x:c>
+      <x:c r="B75" s="15" t="n">
+        <x:v>82010074</x:v>
+      </x:c>
+      <x:c r="C75" s="15" t="n">
+        <x:v>10703173</x:v>
+      </x:c>
+      <x:c r="D75" s="15" t="str">
+        <x:v>星罗分锋·疾锋真意残卷</x:v>
+      </x:c>
+      <x:c r="E75" s="15" t="n">
+        <x:v>101500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="38" customHeight="1">
+      <x:c r="A76" s="15" t="n">
+        <x:v>92010075</x:v>
+      </x:c>
+      <x:c r="B76" s="15" t="n">
+        <x:v>82010075</x:v>
+      </x:c>
+      <x:c r="C76" s="15" t="n">
+        <x:v>10703174</x:v>
+      </x:c>
+      <x:c r="D76" s="15" t="str">
+        <x:v>星罗分锋·蓄锋真意残卷</x:v>
+      </x:c>
+      <x:c r="E76" s="15" t="n">
+        <x:v>101500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="38" customHeight="1">
+      <x:c r="A77" s="15" t="n">
+        <x:v>92010076</x:v>
+      </x:c>
+      <x:c r="B77" s="15" t="n">
+        <x:v>82010076</x:v>
+      </x:c>
+      <x:c r="C77" s="15" t="n">
+        <x:v>10703175</x:v>
+      </x:c>
+      <x:c r="D77" s="15" t="str">
+        <x:v>青息回元·群息真意残卷</x:v>
+      </x:c>
+      <x:c r="E77" s="15" t="n">
+        <x:v>101600</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="38" customHeight="1">
+      <x:c r="A78" s="15" t="n">
+        <x:v>92010077</x:v>
+      </x:c>
+      <x:c r="B78" s="15" t="n">
+        <x:v>82010077</x:v>
+      </x:c>
+      <x:c r="C78" s="15" t="n">
+        <x:v>10703176</x:v>
+      </x:c>
+      <x:c r="D78" s="15" t="str">
+        <x:v>青息回元·护元真意残卷</x:v>
+      </x:c>
+      <x:c r="E78" s="15" t="n">
+        <x:v>101600</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="38" customHeight="1">
+      <x:c r="A79" s="15" t="n">
+        <x:v>92010078</x:v>
+      </x:c>
+      <x:c r="B79" s="15" t="n">
+        <x:v>82010078</x:v>
+      </x:c>
+      <x:c r="C79" s="15" t="n">
+        <x:v>10703177</x:v>
+      </x:c>
+      <x:c r="D79" s="15" t="str">
+        <x:v>青息回元·浓息真意残卷</x:v>
+      </x:c>
+      <x:c r="E79" s="15" t="n">
+        <x:v>101600</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="38" customHeight="1">
+      <x:c r="A80" s="15" t="n">
+        <x:v>92010079</x:v>
+      </x:c>
+      <x:c r="B80" s="15" t="n">
+        <x:v>82010079</x:v>
+      </x:c>
+      <x:c r="C80" s="15" t="n">
+        <x:v>10703178</x:v>
+      </x:c>
+      <x:c r="D80" s="15" t="str">
+        <x:v>青息回元·遥息真意残卷</x:v>
+      </x:c>
+      <x:c r="E80" s="15" t="n">
+        <x:v>101600</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="38" customHeight="1">
+      <x:c r="A81" s="15" t="n">
+        <x:v>92010080</x:v>
+      </x:c>
+      <x:c r="B81" s="15" t="n">
+        <x:v>82010080</x:v>
+      </x:c>
+      <x:c r="C81" s="15" t="n">
+        <x:v>10703179</x:v>
+      </x:c>
+      <x:c r="D81" s="15" t="str">
+        <x:v>青息回元·回息真意残卷</x:v>
+      </x:c>
+      <x:c r="E81" s="15" t="n">
+        <x:v>101600</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="38" customHeight="1">
+      <x:c r="A82" s="15" t="n">
+        <x:v>92010081</x:v>
+      </x:c>
+      <x:c r="B82" s="15" t="n">
+        <x:v>82010081</x:v>
+      </x:c>
+      <x:c r="C82" s="15" t="n">
+        <x:v>10703180</x:v>
+      </x:c>
+      <x:c r="D82" s="15" t="str">
+        <x:v>春脉绵生·延春真意残卷</x:v>
+      </x:c>
+      <x:c r="E82" s="15" t="n">
+        <x:v>101700</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="38" customHeight="1">
+      <x:c r="A83" s="15" t="n">
+        <x:v>92010082</x:v>
+      </x:c>
+      <x:c r="B83" s="15" t="n">
+        <x:v>82010082</x:v>
+      </x:c>
+      <x:c r="C83" s="15" t="n">
+        <x:v>10703181</x:v>
+      </x:c>
+      <x:c r="D83" s="15" t="str">
+        <x:v>春脉绵生·密春真意残卷</x:v>
+      </x:c>
+      <x:c r="E83" s="15" t="n">
+        <x:v>101700</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="38" customHeight="1">
+      <x:c r="A84" s="15" t="n">
+        <x:v>92010083</x:v>
+      </x:c>
+      <x:c r="B84" s="15" t="n">
+        <x:v>82010083</x:v>
+      </x:c>
+      <x:c r="C84" s="15" t="n">
+        <x:v>10703182</x:v>
+      </x:c>
+      <x:c r="D84" s="15" t="str">
+        <x:v>春脉绵生·润脉真意残卷</x:v>
+      </x:c>
+      <x:c r="E84" s="15" t="n">
+        <x:v>101700</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="38" customHeight="1">
+      <x:c r="A85" s="15" t="n">
+        <x:v>92010084</x:v>
+      </x:c>
+      <x:c r="B85" s="15" t="n">
+        <x:v>82010084</x:v>
+      </x:c>
+      <x:c r="C85" s="15" t="n">
+        <x:v>10703183</x:v>
+      </x:c>
+      <x:c r="D85" s="15" t="str">
+        <x:v>春脉绵生·遥春真意残卷</x:v>
+      </x:c>
+      <x:c r="E85" s="15" t="n">
+        <x:v>101700</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="38" customHeight="1">
+      <x:c r="A86" s="15" t="n">
+        <x:v>92010085</x:v>
+      </x:c>
+      <x:c r="B86" s="15" t="n">
+        <x:v>82010085</x:v>
+      </x:c>
+      <x:c r="C86" s="15" t="n">
+        <x:v>10703184</x:v>
+      </x:c>
+      <x:c r="D86" s="15" t="str">
+        <x:v>春脉绵生·春回真意残卷</x:v>
+      </x:c>
+      <x:c r="E86" s="15" t="n">
+        <x:v>101700</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="28" customHeight="1">
+      <x:c r="A87" s="15" t="n">
+        <x:v>92010086</x:v>
+      </x:c>
+      <x:c r="B87" s="15" t="n">
+        <x:v>82010086</x:v>
+      </x:c>
+      <x:c r="C87" s="15" t="n">
+        <x:v>10703185</x:v>
+      </x:c>
+      <x:c r="D87" t="str" s="15">
+        <x:v>定魄术·双发真意残卷</x:v>
+      </x:c>
+      <x:c r="E87" s="15" t="n">
+        <x:v>101800</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="28" customHeight="1">
+      <x:c r="A88" s="15" t="n">
+        <x:v>92010087</x:v>
+      </x:c>
+      <x:c r="B88" s="15" t="n">
+        <x:v>82010087</x:v>
+      </x:c>
+      <x:c r="C88" s="15" t="n">
+        <x:v>10703186</x:v>
+      </x:c>
+      <x:c r="D88" t="str" s="15">
+        <x:v>定魄术·疾射真意残卷</x:v>
+      </x:c>
+      <x:c r="E88" s="15" t="n">
+        <x:v>101800</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="28" customHeight="1">
+      <x:c r="A89" s="15" t="n">
+        <x:v>92010088</x:v>
+      </x:c>
+      <x:c r="B89" s="15" t="n">
+        <x:v>82010088</x:v>
+      </x:c>
+      <x:c r="C89" s="15" t="n">
+        <x:v>10703187</x:v>
+      </x:c>
+      <x:c r="D89" t="str" s="15">
+        <x:v>定魄术·远引真意残卷</x:v>
+      </x:c>
+      <x:c r="E89" s="15" t="n">
+        <x:v>101800</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="28" customHeight="1">
+      <x:c r="A90" s="15" t="n">
+        <x:v>92010089</x:v>
+      </x:c>
+      <x:c r="B90" s="15" t="n">
+        <x:v>82010089</x:v>
+      </x:c>
+      <x:c r="C90" s="15" t="n">
+        <x:v>10703188</x:v>
+      </x:c>
+      <x:c r="D90" t="str" s="15">
+        <x:v>定魄术·回转真意残卷</x:v>
+      </x:c>
+      <x:c r="E90" s="15" t="n">
+        <x:v>101800</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="28" customHeight="1">
+      <x:c r="A91" s="15" t="n">
+        <x:v>92010090</x:v>
+      </x:c>
+      <x:c r="B91" s="15" t="n">
+        <x:v>82010090</x:v>
+      </x:c>
+      <x:c r="C91" s="15" t="n">
+        <x:v>10703189</x:v>
+      </x:c>
+      <x:c r="D91" t="str" s="15">
+        <x:v>定魄术·广域真意残卷</x:v>
+      </x:c>
+      <x:c r="E91" s="15" t="n">
+        <x:v>101800</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="38" customHeight="1">
+      <x:c r="A92" s="15" t="n">
+        <x:v>92010091</x:v>
+      </x:c>
+      <x:c r="B92" s="15" t="n">
+        <x:v>82010091</x:v>
+      </x:c>
+      <x:c r="C92" s="15" t="n">
+        <x:v>10703190</x:v>
+      </x:c>
+      <x:c r="D92" s="15" t="str">
+        <x:v>霜锁九脉·广霜真意残卷</x:v>
+      </x:c>
+      <x:c r="E92" s="15" t="n">
+        <x:v>101900</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="38" customHeight="1">
+      <x:c r="A93" s="15" t="n">
+        <x:v>92010092</x:v>
+      </x:c>
+      <x:c r="B93" s="15" t="n">
+        <x:v>82010092</x:v>
+      </x:c>
+      <x:c r="C93" s="15" t="n">
+        <x:v>10703191</x:v>
+      </x:c>
+      <x:c r="D93" s="15" t="str">
+        <x:v>霜锁九脉·凝霜真意残卷</x:v>
+      </x:c>
+      <x:c r="E93" s="15" t="n">
+        <x:v>101900</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="38" customHeight="1">
+      <x:c r="A94" s="15" t="n">
+        <x:v>92010093</x:v>
+      </x:c>
+      <x:c r="B94" s="15" t="n">
+        <x:v>82010093</x:v>
+      </x:c>
+      <x:c r="C94" s="15" t="n">
+        <x:v>10703192</x:v>
+      </x:c>
+      <x:c r="D94" s="15" t="str">
+        <x:v>霜锁九脉·遥霜真意残卷</x:v>
+      </x:c>
+      <x:c r="E94" s="15" t="n">
+        <x:v>101900</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="38" customHeight="1">
+      <x:c r="A95" s="15" t="n">
+        <x:v>92010094</x:v>
+      </x:c>
+      <x:c r="B95" s="15" t="n">
+        <x:v>82010094</x:v>
+      </x:c>
+      <x:c r="C95" s="15" t="n">
+        <x:v>10703193</x:v>
+      </x:c>
+      <x:c r="D95" s="15" t="str">
+        <x:v>霜锁九脉·回霜真意残卷</x:v>
+      </x:c>
+      <x:c r="E95" s="15" t="n">
+        <x:v>101900</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="38" customHeight="1">
+      <x:c r="A96" s="15" t="n">
+        <x:v>92010095</x:v>
+      </x:c>
+      <x:c r="B96" s="15" t="n">
+        <x:v>82010095</x:v>
+      </x:c>
+      <x:c r="C96" s="15" t="n">
+        <x:v>10703194</x:v>
+      </x:c>
+      <x:c r="D96" s="15" t="str">
+        <x:v>霜锁九脉·寒蚀真意残卷</x:v>
+      </x:c>
+      <x:c r="E96" s="15" t="n">
+        <x:v>101900</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="28" customHeight="1">
+      <x:c r="A97" s="15" t="n">
+        <x:v>92010096</x:v>
+      </x:c>
+      <x:c r="B97" s="15" t="n">
+        <x:v>82010096</x:v>
+      </x:c>
+      <x:c r="C97" s="15" t="n">
+        <x:v>10703195</x:v>
+      </x:c>
+      <x:c r="D97" s="15" t="str">
+        <x:v>砺锋诀·久锋真意残卷</x:v>
+      </x:c>
+      <x:c r="E97" s="15" t="n">
+        <x:v>102000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="28" customHeight="1">
+      <x:c r="A98" s="15" t="n">
+        <x:v>92010097</x:v>
+      </x:c>
+      <x:c r="B98" s="15" t="n">
+        <x:v>82010097</x:v>
+      </x:c>
+      <x:c r="C98" s="15" t="n">
+        <x:v>10703196</x:v>
+      </x:c>
+      <x:c r="D98" s="15" t="str">
+        <x:v>砺锋诀·锐锋真意残卷</x:v>
+      </x:c>
+      <x:c r="E98" s="15" t="n">
+        <x:v>102000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="28" customHeight="1">
+      <x:c r="A99" s="15" t="n">
+        <x:v>92010098</x:v>
+      </x:c>
+      <x:c r="B99" s="15" t="n">
+        <x:v>82010098</x:v>
+      </x:c>
+      <x:c r="C99" s="15" t="n">
+        <x:v>10703197</x:v>
+      </x:c>
+      <x:c r="D99" s="15" t="str">
+        <x:v>砺锋诀·回锋真意残卷</x:v>
+      </x:c>
+      <x:c r="E99" s="15" t="n">
+        <x:v>102000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="28" customHeight="1">
+      <x:c r="A100" s="15" t="n">
+        <x:v>92010099</x:v>
+      </x:c>
+      <x:c r="B100" s="15" t="n">
+        <x:v>82010099</x:v>
+      </x:c>
+      <x:c r="C100" s="15" t="n">
+        <x:v>10703198</x:v>
+      </x:c>
+      <x:c r="D100" s="15" t="str">
+        <x:v>砺锋诀·聚锋真意残卷</x:v>
+      </x:c>
+      <x:c r="E100" s="15" t="n">
+        <x:v>102000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="28" customHeight="1">
+      <x:c r="A101" s="15" t="n">
+        <x:v>92010100</x:v>
+      </x:c>
+      <x:c r="B101" s="15" t="n">
+        <x:v>82010100</x:v>
+      </x:c>
+      <x:c r="C101" s="15" t="n">
+        <x:v>10703199</x:v>
+      </x:c>
+      <x:c r="D101" s="15" t="str">
+        <x:v>砺锋诀·护锋真意残卷</x:v>
+      </x:c>
+      <x:c r="E101" s="15" t="n">
+        <x:v>102000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="38" customHeight="1">
+      <x:c r="A102" s="15" t="n">
+        <x:v>92010101</x:v>
+      </x:c>
+      <x:c r="B102" s="15" t="n">
+        <x:v>82010101</x:v>
+      </x:c>
+      <x:c r="C102" s="15" t="n">
+        <x:v>10703200</x:v>
+      </x:c>
+      <x:c r="D102" s="15" t="str">
+        <x:v>玄炁贯灵·久灵真意残卷</x:v>
+      </x:c>
+      <x:c r="E102" s="15" t="n">
+        <x:v>102100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="38" customHeight="1">
+      <x:c r="A103" s="15" t="n">
+        <x:v>92010102</x:v>
+      </x:c>
+      <x:c r="B103" s="15" t="n">
+        <x:v>82010102</x:v>
+      </x:c>
+      <x:c r="C103" s="15" t="n">
+        <x:v>10703201</x:v>
+      </x:c>
+      <x:c r="D103" s="15" t="str">
+        <x:v>玄炁贯灵·贯灵真意残卷</x:v>
+      </x:c>
+      <x:c r="E103" s="15" t="n">
+        <x:v>102100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="38" customHeight="1">
+      <x:c r="A104" s="15" t="n">
+        <x:v>92010103</x:v>
+      </x:c>
+      <x:c r="B104" s="15" t="n">
+        <x:v>82010103</x:v>
+      </x:c>
+      <x:c r="C104" s="15" t="n">
+        <x:v>10703202</x:v>
+      </x:c>
+      <x:c r="D104" s="15" t="str">
+        <x:v>玄炁贯灵·回灵真意残卷</x:v>
+      </x:c>
+      <x:c r="E104" s="15" t="n">
+        <x:v>102100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" ht="38" customHeight="1">
+      <x:c r="A105" s="15" t="n">
+        <x:v>92010104</x:v>
+      </x:c>
+      <x:c r="B105" s="15" t="n">
+        <x:v>82010104</x:v>
+      </x:c>
+      <x:c r="C105" s="15" t="n">
+        <x:v>10703203</x:v>
+      </x:c>
+      <x:c r="D105" s="15" t="str">
+        <x:v>玄炁贯灵·藏灵真意残卷</x:v>
+      </x:c>
+      <x:c r="E105" s="15" t="n">
+        <x:v>102100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="38" customHeight="1">
+      <x:c r="A106" s="15" t="n">
+        <x:v>92010105</x:v>
+      </x:c>
+      <x:c r="B106" s="15" t="n">
+        <x:v>82010105</x:v>
+      </x:c>
+      <x:c r="C106" s="15" t="n">
+        <x:v>10703204</x:v>
+      </x:c>
+      <x:c r="D106" s="15" t="str">
+        <x:v>玄炁贯灵·护灵真意残卷</x:v>
+      </x:c>
+      <x:c r="E106" s="15" t="n">
+        <x:v>102100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="28" customHeight="1">
+      <x:c r="A107" s="15" t="n">
+        <x:v>92010106</x:v>
+      </x:c>
+      <x:c r="B107" s="15" t="n">
+        <x:v>82010106</x:v>
+      </x:c>
+      <x:c r="C107" s="15" t="n">
+        <x:v>10703205</x:v>
+      </x:c>
+      <x:c r="D107" s="15" t="str">
+        <x:v>破甲印·久裂真意残卷</x:v>
+      </x:c>
+      <x:c r="E107" s="15" t="n">
+        <x:v>102200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="28" customHeight="1">
+      <x:c r="A108" s="15" t="n">
+        <x:v>92010107</x:v>
+      </x:c>
+      <x:c r="B108" s="15" t="n">
+        <x:v>82010107</x:v>
+      </x:c>
+      <x:c r="C108" s="15" t="n">
+        <x:v>10703206</x:v>
+      </x:c>
+      <x:c r="D108" s="15" t="str">
+        <x:v>破甲印·深裂真意残卷</x:v>
+      </x:c>
+      <x:c r="E108" s="15" t="n">
+        <x:v>102200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="28" customHeight="1">
+      <x:c r="A109" s="15" t="n">
+        <x:v>92010108</x:v>
+      </x:c>
+      <x:c r="B109" s="15" t="n">
+        <x:v>82010108</x:v>
+      </x:c>
+      <x:c r="C109" s="15" t="n">
+        <x:v>10703207</x:v>
+      </x:c>
+      <x:c r="D109" s="15" t="str">
+        <x:v>破甲印·遥裂真意残卷</x:v>
+      </x:c>
+      <x:c r="E109" s="15" t="n">
+        <x:v>102200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="28" customHeight="1">
+      <x:c r="A110" s="15" t="n">
+        <x:v>92010109</x:v>
+      </x:c>
+      <x:c r="B110" s="15" t="n">
+        <x:v>82010109</x:v>
+      </x:c>
+      <x:c r="C110" s="15" t="n">
+        <x:v>10703208</x:v>
+      </x:c>
+      <x:c r="D110" s="15" t="str">
+        <x:v>破甲印·回裂真意残卷</x:v>
+      </x:c>
+      <x:c r="E110" s="15" t="n">
+        <x:v>102200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="28" customHeight="1">
+      <x:c r="A111" s="15" t="n">
+        <x:v>92010110</x:v>
+      </x:c>
+      <x:c r="B111" s="15" t="n">
+        <x:v>82010110</x:v>
+      </x:c>
+      <x:c r="C111" s="15" t="n">
+        <x:v>10703209</x:v>
+      </x:c>
+      <x:c r="D111" s="15" t="str">
+        <x:v>破甲印·群裂真意残卷</x:v>
+      </x:c>
+      <x:c r="E111" s="15" t="n">
+        <x:v>102200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="28" customHeight="1">
+      <x:c r="A112" s="15" t="n">
+        <x:v>92010111</x:v>
+      </x:c>
+      <x:c r="B112" s="15" t="n">
+        <x:v>82010111</x:v>
+      </x:c>
+      <x:c r="C112" s="15" t="n">
+        <x:v>10703210</x:v>
+      </x:c>
+      <x:c r="D112" s="15" t="str">
+        <x:v>蚀法咒·久蚀真意残卷</x:v>
+      </x:c>
+      <x:c r="E112" s="15" t="n">
+        <x:v>102300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="28" customHeight="1">
+      <x:c r="A113" s="15" t="n">
+        <x:v>92010112</x:v>
+      </x:c>
+      <x:c r="B113" s="15" t="n">
+        <x:v>82010112</x:v>
+      </x:c>
+      <x:c r="C113" s="15" t="n">
+        <x:v>10703211</x:v>
+      </x:c>
+      <x:c r="D113" s="15" t="str">
+        <x:v>蚀法咒·深蚀真意残卷</x:v>
+      </x:c>
+      <x:c r="E113" s="15" t="n">
+        <x:v>102300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="28" customHeight="1">
+      <x:c r="A114" s="15" t="n">
+        <x:v>92010113</x:v>
+      </x:c>
+      <x:c r="B114" s="15" t="n">
+        <x:v>82010113</x:v>
+      </x:c>
+      <x:c r="C114" s="15" t="n">
+        <x:v>10703212</x:v>
+      </x:c>
+      <x:c r="D114" s="15" t="str">
+        <x:v>蚀法咒·遥蚀真意残卷</x:v>
+      </x:c>
+      <x:c r="E114" s="15" t="n">
+        <x:v>102300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="28" customHeight="1">
+      <x:c r="A115" s="15" t="n">
+        <x:v>92010114</x:v>
+      </x:c>
+      <x:c r="B115" s="15" t="n">
+        <x:v>82010114</x:v>
+      </x:c>
+      <x:c r="C115" s="15" t="n">
+        <x:v>10703213</x:v>
+      </x:c>
+      <x:c r="D115" s="15" t="str">
+        <x:v>蚀法咒·回蚀真意残卷</x:v>
+      </x:c>
+      <x:c r="E115" s="15" t="n">
+        <x:v>102300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="28" customHeight="1">
+      <x:c r="A116" s="15" t="n">
+        <x:v>92010115</x:v>
+      </x:c>
+      <x:c r="B116" s="15" t="n">
+        <x:v>82010115</x:v>
+      </x:c>
+      <x:c r="C116" s="15" t="n">
+        <x:v>10703214</x:v>
+      </x:c>
+      <x:c r="D116" s="15" t="str">
+        <x:v>蚀法咒·群蚀真意残卷</x:v>
+      </x:c>
+      <x:c r="E116" s="15" t="n">
+        <x:v>102300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="38" customHeight="1">
+      <x:c r="A117" s="15" t="n">
+        <x:v>92010116</x:v>
+      </x:c>
+      <x:c r="B117" s="15" t="n">
+        <x:v>82010116</x:v>
+      </x:c>
+      <x:c r="C117" s="15" t="n">
+        <x:v>10703215</x:v>
+      </x:c>
+      <x:c r="D117" s="15" t="str">
+        <x:v>余烬侵脉·青木真意残卷</x:v>
+      </x:c>
+      <x:c r="E117" s="15" t="n">
+        <x:v>102400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="38" customHeight="1">
+      <x:c r="A118" s="15" t="n">
+        <x:v>92010117</x:v>
+      </x:c>
+      <x:c r="B118" s="15" t="n">
+        <x:v>82010117</x:v>
+      </x:c>
+      <x:c r="C118" s="15" t="n">
+        <x:v>10703216</x:v>
+      </x:c>
+      <x:c r="D118" s="15" t="str">
+        <x:v>余烬侵脉·庚金真意残卷</x:v>
+      </x:c>
+      <x:c r="E118" s="15" t="n">
+        <x:v>102400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" ht="38" customHeight="1">
+      <x:c r="A119" s="15" t="n">
+        <x:v>92010118</x:v>
+      </x:c>
+      <x:c r="B119" s="15" t="n">
+        <x:v>82010118</x:v>
+      </x:c>
+      <x:c r="C119" s="15" t="n">
+        <x:v>10703217</x:v>
+      </x:c>
+      <x:c r="D119" s="15" t="str">
+        <x:v>余烬侵脉·久烬真意残卷</x:v>
+      </x:c>
+      <x:c r="E119" s="15" t="n">
+        <x:v>102400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="38" customHeight="1">
+      <x:c r="A120" s="15" t="n">
+        <x:v>92010119</x:v>
+      </x:c>
+      <x:c r="B120" s="15" t="n">
+        <x:v>82010119</x:v>
+      </x:c>
+      <x:c r="C120" s="15" t="n">
+        <x:v>10703218</x:v>
+      </x:c>
+      <x:c r="D120" s="15" t="str">
+        <x:v>余烬侵脉·炽烬真意残卷</x:v>
+      </x:c>
+      <x:c r="E120" s="15" t="n">
+        <x:v>102400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="38" customHeight="1">
+      <x:c r="A121" s="15" t="n">
+        <x:v>92010120</x:v>
+      </x:c>
+      <x:c r="B121" s="15" t="n">
+        <x:v>82010120</x:v>
+      </x:c>
+      <x:c r="C121" s="15" t="n">
+        <x:v>10703219</x:v>
+      </x:c>
+      <x:c r="D121" s="15" t="str">
+        <x:v>余烬侵脉·急烬真意残卷</x:v>
+      </x:c>
+      <x:c r="E121" s="15" t="n">
+        <x:v>102400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" ht="38" customHeight="1">
+      <x:c r="A122" s="15" t="n">
+        <x:v>92010121</x:v>
+      </x:c>
+      <x:c r="B122" s="15" t="n">
+        <x:v>82010121</x:v>
+      </x:c>
+      <x:c r="C122" s="15" t="n">
+        <x:v>10703220</x:v>
+      </x:c>
+      <x:c r="D122" s="15" t="str">
+        <x:v>离焰周身·庚金真意残卷</x:v>
+      </x:c>
+      <x:c r="E122" s="15" t="n">
+        <x:v>102500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="38" customHeight="1">
+      <x:c r="A123" s="15" t="n">
+        <x:v>92010122</x:v>
+      </x:c>
+      <x:c r="B123" s="15" t="n">
+        <x:v>82010122</x:v>
+      </x:c>
+      <x:c r="C123" s="15" t="n">
+        <x:v>10703221</x:v>
+      </x:c>
+      <x:c r="D123" s="15" t="str">
+        <x:v>离焰周身·玄水真意残卷</x:v>
+      </x:c>
+      <x:c r="E123" s="15" t="n">
+        <x:v>102500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" ht="38" customHeight="1">
+      <x:c r="A124" s="15" t="n">
+        <x:v>92010123</x:v>
+      </x:c>
+      <x:c r="B124" s="15" t="n">
+        <x:v>82010123</x:v>
+      </x:c>
+      <x:c r="C124" s="15" t="n">
+        <x:v>10703222</x:v>
+      </x:c>
+      <x:c r="D124" s="15" t="str">
+        <x:v>离焰周身·久焰真意残卷</x:v>
+      </x:c>
+      <x:c r="E124" s="15" t="n">
+        <x:v>102500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" ht="38" customHeight="1">
+      <x:c r="A125" s="15" t="n">
+        <x:v>92010124</x:v>
+      </x:c>
+      <x:c r="B125" s="15" t="n">
+        <x:v>82010124</x:v>
+      </x:c>
+      <x:c r="C125" s="15" t="n">
+        <x:v>10703223</x:v>
+      </x:c>
+      <x:c r="D125" s="15" t="str">
+        <x:v>离焰周身·急焰真意残卷</x:v>
+      </x:c>
+      <x:c r="E125" s="15" t="n">
+        <x:v>102500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" ht="38" customHeight="1">
+      <x:c r="A126" s="15" t="n">
+        <x:v>92010125</x:v>
+      </x:c>
+      <x:c r="B126" s="15" t="n">
+        <x:v>82010125</x:v>
+      </x:c>
+      <x:c r="C126" s="15" t="n">
+        <x:v>10703224</x:v>
+      </x:c>
+      <x:c r="D126" s="15" t="str">
+        <x:v>离焰周身·回焰真意残卷</x:v>
+      </x:c>
+      <x:c r="E126" s="15" t="n">
+        <x:v>102500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" ht="38" customHeight="1">
+      <x:c r="A127" s="15" t="n">
+        <x:v>92010126</x:v>
+      </x:c>
+      <x:c r="B127" s="15" t="n">
+        <x:v>82010126</x:v>
+      </x:c>
+      <x:c r="C127" s="15" t="n">
+        <x:v>10703225</x:v>
+      </x:c>
+      <x:c r="D127" s="15" t="str">
+        <x:v>玄霜蚀法·久环真意残卷</x:v>
+      </x:c>
+      <x:c r="E127" s="15" t="n">
+        <x:v>102600</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" ht="38" customHeight="1">
+      <x:c r="A128" s="15" t="n">
+        <x:v>92010127</x:v>
+      </x:c>
+      <x:c r="B128" s="15" t="n">
+        <x:v>82010127</x:v>
+      </x:c>
+      <x:c r="C128" s="15" t="n">
+        <x:v>10703226</x:v>
+      </x:c>
+      <x:c r="D128" s="15" t="str">
+        <x:v>玄霜蚀法·急环真意残卷</x:v>
+      </x:c>
+      <x:c r="E128" s="15" t="n">
+        <x:v>102600</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" ht="38" customHeight="1">
+      <x:c r="A129" s="15" t="n">
+        <x:v>92010128</x:v>
+      </x:c>
+      <x:c r="B129" s="15" t="n">
+        <x:v>82010128</x:v>
+      </x:c>
+      <x:c r="C129" s="15" t="n">
+        <x:v>10703227</x:v>
+      </x:c>
+      <x:c r="D129" s="15" t="str">
+        <x:v>玄霜蚀法·回环真意残卷</x:v>
+      </x:c>
+      <x:c r="E129" s="15" t="n">
+        <x:v>102600</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" ht="38" customHeight="1">
+      <x:c r="A130" s="15" t="n">
+        <x:v>92010129</x:v>
+      </x:c>
+      <x:c r="B130" s="15" t="n">
+        <x:v>82010129</x:v>
+      </x:c>
+      <x:c r="C130" s="15" t="n">
+        <x:v>10703228</x:v>
+      </x:c>
+      <x:c r="D130" s="15" t="str">
+        <x:v>玄霜蚀法·蓄环真意残卷</x:v>
+      </x:c>
+      <x:c r="E130" s="15" t="n">
+        <x:v>102600</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" ht="38" customHeight="1">
+      <x:c r="A131" s="15" t="n">
+        <x:v>92010130</x:v>
+      </x:c>
+      <x:c r="B131" s="15" t="n">
+        <x:v>82010130</x:v>
+      </x:c>
+      <x:c r="C131" s="15" t="n">
+        <x:v>10703229</x:v>
+      </x:c>
+      <x:c r="D131" s="15" t="str">
+        <x:v>玄霜蚀法·凝护真意残卷</x:v>
+      </x:c>
+      <x:c r="E131" s="15" t="n">
+        <x:v>102600</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" ht="38" customHeight="1">
+      <x:c r="A132" s="15" t="n">
+        <x:v>92010131</x:v>
+      </x:c>
+      <x:c r="B132" s="15" t="n">
+        <x:v>82010131</x:v>
+      </x:c>
+      <x:c r="C132" s="15" t="n">
+        <x:v>10703230</x:v>
+      </x:c>
+      <x:c r="D132" s="15" t="str">
+        <x:v>坤岳辟界阵·久阵真意残卷</x:v>
+      </x:c>
+      <x:c r="E132" s="15" t="n">
+        <x:v>102700</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" ht="38" customHeight="1">
+      <x:c r="A133" s="15" t="n">
+        <x:v>92010132</x:v>
+      </x:c>
+      <x:c r="B133" s="15" t="n">
+        <x:v>82010132</x:v>
+      </x:c>
+      <x:c r="C133" s="15" t="n">
+        <x:v>10703231</x:v>
+      </x:c>
+      <x:c r="D133" s="15" t="str">
+        <x:v>坤岳辟界阵·急阵真意残卷</x:v>
+      </x:c>
+      <x:c r="E133" s="15" t="n">
+        <x:v>102700</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" ht="38" customHeight="1">
+      <x:c r="A134" s="15" t="n">
+        <x:v>92010133</x:v>
+      </x:c>
+      <x:c r="B134" s="15" t="n">
+        <x:v>82010133</x:v>
+      </x:c>
+      <x:c r="C134" s="15" t="n">
+        <x:v>10703232</x:v>
+      </x:c>
+      <x:c r="D134" s="15" t="str">
+        <x:v>坤岳辟界阵·回阵真意残卷</x:v>
+      </x:c>
+      <x:c r="E134" s="15" t="n">
+        <x:v>102700</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" ht="38" customHeight="1">
+      <x:c r="A135" s="15" t="n">
+        <x:v>92010134</x:v>
+      </x:c>
+      <x:c r="B135" s="15" t="n">
+        <x:v>82010134</x:v>
+      </x:c>
+      <x:c r="C135" s="15" t="n">
+        <x:v>10703233</x:v>
+      </x:c>
+      <x:c r="D135" s="15" t="str">
+        <x:v>坤岳辟界阵·蓄阵真意残卷</x:v>
+      </x:c>
+      <x:c r="E135" s="15" t="n">
+        <x:v>102700</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" ht="38" customHeight="1">
+      <x:c r="A136" s="15" t="n">
+        <x:v>92010135</x:v>
+      </x:c>
+      <x:c r="B136" s="15" t="n">
+        <x:v>82010135</x:v>
+      </x:c>
+      <x:c r="C136" s="15" t="n">
+        <x:v>10703234</x:v>
+      </x:c>
+      <x:c r="D136" s="15" t="str">
+        <x:v>坤岳辟界阵·壁阵真意残卷</x:v>
+      </x:c>
+      <x:c r="E136" s="15" t="n">
+        <x:v>102700</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" ht="38" customHeight="1">
+      <x:c r="A137" s="15" t="n">
+        <x:v>92010136</x:v>
+      </x:c>
+      <x:c r="B137" s="15" t="n">
+        <x:v>82010136</x:v>
+      </x:c>
+      <x:c r="C137" s="15" t="n">
+        <x:v>10703235</x:v>
+      </x:c>
+      <x:c r="D137" s="15" t="str">
+        <x:v>游身九转·远游真意残卷</x:v>
+      </x:c>
+      <x:c r="E137" s="15" t="n">
+        <x:v>102800</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" ht="38" customHeight="1">
+      <x:c r="A138" s="15" t="n">
+        <x:v>92010137</x:v>
+      </x:c>
+      <x:c r="B138" s="15" t="n">
+        <x:v>82010137</x:v>
+      </x:c>
+      <x:c r="C138" s="15" t="n">
+        <x:v>10703236</x:v>
+      </x:c>
+      <x:c r="D138" s="15" t="str">
+        <x:v>游身九转·疾游真意残卷</x:v>
+      </x:c>
+      <x:c r="E138" s="15" t="n">
+        <x:v>102800</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" ht="38" customHeight="1">
+      <x:c r="A139" s="15" t="n">
+        <x:v>92010138</x:v>
+      </x:c>
+      <x:c r="B139" s="15" t="n">
+        <x:v>82010138</x:v>
+      </x:c>
+      <x:c r="C139" s="15" t="n">
+        <x:v>10703237</x:v>
+      </x:c>
+      <x:c r="D139" s="15" t="str">
+        <x:v>游身九转·回游真意残卷</x:v>
+      </x:c>
+      <x:c r="E139" s="15" t="n">
+        <x:v>102800</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" ht="38" customHeight="1">
+      <x:c r="A140" s="15" t="n">
+        <x:v>92010139</x:v>
+      </x:c>
+      <x:c r="B140" s="15" t="n">
+        <x:v>82010139</x:v>
+      </x:c>
+      <x:c r="C140" s="15" t="n">
+        <x:v>10703238</x:v>
+      </x:c>
+      <x:c r="D140" s="15" t="str">
+        <x:v>游身九转·双游真意残卷</x:v>
+      </x:c>
+      <x:c r="E140" s="15" t="n">
+        <x:v>102800</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" ht="38" customHeight="1">
+      <x:c r="A141" s="15" t="n">
+        <x:v>92010140</x:v>
+      </x:c>
+      <x:c r="B141" s="15" t="n">
+        <x:v>82010140</x:v>
+      </x:c>
+      <x:c r="C141" s="15" t="n">
+        <x:v>10703239</x:v>
+      </x:c>
+      <x:c r="D141" s="15" t="str">
+        <x:v>游身九转·护游真意残卷</x:v>
+      </x:c>
+      <x:c r="E141" s="15" t="n">
+        <x:v>102800</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>